--- a/translations.xlsx
+++ b/translations.xlsx
@@ -10,6 +10,8 @@
     <sheet name="UI text" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Parties" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="MP names" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Institutions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Case types" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7865,4 +7867,654 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Влада на Република Северна Македонија</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Qeveria e Republikës së Maqedonisë së Veriut</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Government of the Republic of North Macedonia</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Претседател на Владата на Република Северна Македонија</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kryeministri i Republikës së Maqedonisë së Veriut</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prime Minister of the Republic of North Macedonia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Министерство за дигитална трансформација</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ministria e Transformimit Digjital</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ministry of Digital Transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Министерство за европски прашања</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ministria e Çështjeve Evropiane</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ministry of European Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Министерство за економија и труд</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ministria e Ekonomisë dhe Punës</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ministry of Economy and Labour</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Министерство за енергетика, рударство и минерални суровини</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ministria e Energjetikës, Minierave dhe Lëndëve të Para Minerale</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ministry of Energy, Mining and Mineral Resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Министерство за животна средина и просторно планирање</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ministria e Mjedisit Jetësor dhe Planifikimit Hapësinor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ministry of Environment and Spatial Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Министерство за здравство</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ministria e Shëndetësisë</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ministry of Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Министерство за земјоделство, шумарство и водостопанство</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ministria e Bujqësisë, Pylltarisë dhe Ekonomisë së Ujërave</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture, Forestry and Water Economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Министерство за култура и туризам</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ministria e Kulturës dhe Turizmit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ministry of Culture and Tourism</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Министерство за локална самоуправа</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ministria e Vetëqeverisjes Lokale</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ministry of Local Self-Government</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Министерство за образование и наука</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ministria e Arsimit dhe Shkencës</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ministry of Education and Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Министерство за одбрана</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ministria e Mbrojtjes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ministry of Defence</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Министерство за односи меѓу заедниците</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ministria e Marrëdhënieve ndërmjet Bashkësive</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ministry of Relations between Communities</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Министерство за правда</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ministria e Drejtësisë</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ministry of Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Министерство за социјална политика, демографија и млади</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ministria e Politikës Sociale, Demografisë dhe Rinisë</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ministry of Social Policy, Demography and Youth</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Министерство за транспорт</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ministria e Transportit</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ministry of Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Министерство за труд и социјална политика</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ministria e Punës dhe Politikës Sociale</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ministry of Labour and Social Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Министерство за финансии</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ministria e Financave</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ministry of Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Министерство за јавна администрација</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ministria e Administratës Publike</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ministry of Public Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Министерството за внатрешни работи</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ministria e Punëve të Brendshme</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ministry of Internal Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Министерството за надворешни работи и надворешна трговија</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ministria e Punëve të Jashtme dhe Tregtisë së Jashtme</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ministry of Foreign Affairs and Foreign Trade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Работен однос и права од работен однос</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Marrëdhënia e punës dhe të drejtat nga marrëdhënia e punës</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Employment and labour rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Транспорт и инфраструктура</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Transporti dhe infrastruktura</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Transport and infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Животна средина</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mjedisi jetësor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Социјални услуги</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Shërbimet sociale</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Social services</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Правна помош</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ndihma juridike</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Legal aid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Здравствена заштита</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mbrojtja shëndetësore</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arsimi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Иницијативи за развој на заедницата</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nismat për zhvillimin e bashkësisë</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Community development initiatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Пристап до јавни услуги</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Qasja në shërbimet publike</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Access to public services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Домување</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Banimi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Финансии и буџет</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Financat dhe buxheti</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Finance and budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Актуелно законодавство и владини политики</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Legjislacioni aktual dhe politikat qeveritare</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Current legislation and government policies</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/translations.xlsx
+++ b/translations.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D212"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Për projektin</t>
+          <t>Rreth projektit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Për IDSCS</t>
+          <t>Rreth IDSCS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Filtri</t>
+          <t>Filtër</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Të mëparshmet</t>
+          <t>Të mëparshme</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Të mëtejshmet</t>
+          <t>Të mëtejshme</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pyetja</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2134,2968 +2134,2986 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mymp.title</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Активност на пратеник</t>
-        </is>
-      </c>
+          <t>questions.aiTranslationNotice</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetit</t>
+          <t>Përkthimi në gjuhën shqipe i pyetjeve parlamentare është përgatitur me ndihmën e mjeteve të inteligjencës artificiale (AI), duke u bazuar në materialet e disponueshme në gjuhën maqedonase në Portalin e të Dhënave të Hapura të Kuvendit. Deri në ditën e publikimit, materialet në portal ishin të disponueshme vetëm në gjuhën maqedonase.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>MP activity</t>
+          <t>The English translation of the parliamentary questions was prepared using artificial intelligence (AI) tools, based on the materials available in Macedonian on the Assembly Open Data Portal. As of the date of publication, the materials on the portal were available only in Macedonian.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mymp.subtitle</t>
+          <t>mymp.title</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
+          <t>Активност на пратеник</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
+          <t>Aktiviteti i deputetit</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MP activity for the period January–June 2025</t>
+          <t>MP activity</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mymp.stalenessNote</t>
+          <t>mymp.subtitle</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
+          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
+          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
+          <t>MP activity for the period January–June 2025</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mymp.mostActiveTitle</t>
+          <t>mymp.stalenessNote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Најактивен пратеник</t>
+          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Deputeti më aktiv</t>
+          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Most active MP</t>
+          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mymp.mostActiveNote</t>
+          <t>mymp.mostActiveTitle</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
+          <t>Најактивен пратеник</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
+          <t>Deputeti më aktiv</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
+          <t>Most active MP</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mymp.kpiMPs</t>
+          <t>mymp.mostActiveNote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mymp.newlySeatedNote</t>
+          <t>mymp.kpiMPs</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>стапиле на должност по периодот на извештајот</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>kanë marrë mandatin pas periudhës së raportit</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>took office after the reporting period</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mymp.noPeriodData</t>
+          <t>mymp.newlySeatedNote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Стапил на должност по последниот извештај за активност</t>
+          <t>стапиле на должност по периодот на извештајот</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
+          <t>kanë marrë mandatin pas periudhës së raportit</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Took office after the latest activity report</t>
+          <t>took office after the reporting period</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mymp.kpiAvgAttendance</t>
+          <t>mymp.noPeriodData</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Просечно присуство</t>
+          <t>Стапил на должност по последниот извештај за активност</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prezenca mesatare</t>
+          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Average attendance</t>
+          <t>Took office after the latest activity report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mymp.kpiZeroQuestions</t>
+          <t>mymp.kpiAvgAttendance</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Пратеници без прашања</t>
+          <t>Просечно присуство</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Deputetë pa pyetje</t>
+          <t>Prezenca mesatare</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MPs with no questions</t>
+          <t>Average attendance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mymp.chartAttendance</t>
+          <t>mymp.kpiZeroQuestions</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Пратеници без прашања</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Deputetë pa pyetje</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>MPs with no questions</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mymp.chartDiscussions</t>
+          <t>mymp.chartAttendance</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mymp.chartQuestions</t>
+          <t>mymp.chartDiscussions</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mymp.colMP</t>
+          <t>mymp.chartQuestions</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Пратеник</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Deputeti</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mymp.colAttendance</t>
+          <t>mymp.colMP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Пратеник</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Deputeti</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mymp.colExcused</t>
+          <t>mymp.colAttendance</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Оправдано отсуство</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mungesa e justifikuar</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Excused absence</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mymp.colUnexcused</t>
+          <t>mymp.colExcused</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Неоправдано отсуство</t>
+          <t>Оправдано отсуство</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mungesa e pajustifikuar</t>
+          <t>Mungesë e arsyetuar</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Unexcused absence</t>
+          <t>Excused absence</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mymp.colDiscussions</t>
+          <t>mymp.colUnexcused</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Неоправдано отсуство</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Mungesa e pa arsyetuar</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Unexcused absence</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mymp.colLaws</t>
+          <t>mymp.colDiscussions</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mymp.colAmendments</t>
+          <t>mymp.colLaws</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mymp.colQuestions</t>
+          <t>mymp.colAmendments</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Прашања</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pyetje</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mymp.colCommittees</t>
+          <t>mymp.colQuestions</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Прашања</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Questions</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mymp.zeroQuestionsLabel</t>
+          <t>mymp.colCommittees</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Пратеници кои не поставиле ниту едно прашање</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>MPs who asked no questions at all</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mymp.top5Title</t>
+          <t>mymp.zeroQuestionsLabel</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Топ 5 најактивни пратеници</t>
+          <t>Пратеници кои не поставиле ниту едно прашање</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Top 5 deputetët më aktivë</t>
+          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Top 5 most active MPs</t>
+          <t>MPs who asked no questions at all</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mymp.top15Label</t>
+          <t>mymp.top5Title</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Топ 15 —</t>
+          <t>Топ 5 најактивни пратеници</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>Top 5 deputetët më aktivë</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>Top 5 most active MPs</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mymp.compositeLabel</t>
+          <t>mymp.top15Label</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Вкупна активност</t>
+          <t>Топ 15 —</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Top 15 —</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>Top 15 —</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mymp.onlyZero</t>
+          <t>mymp.compositeLabel</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Само без прашања</t>
+          <t>Вкупна активност</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Vetëm pa pyetje</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Only without questions</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mymp.zeroSentence</t>
+          <t>mymp.onlyZero</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
+          <t>Само без прашања</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
+          <t>Vetëm pa pyetje</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
+          <t>Only without questions</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mymp.periodLabel</t>
+          <t>mymp.zeroSentence</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Период</t>
+          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Periudha</t>
+          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>offices.title</t>
+          <t>mymp.periodLabel</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>Период</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>Periudha</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>Period</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>offices.subtitle</t>
+          <t>offices.title</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>offices.kpiCases</t>
+          <t>offices.subtitle</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Случаи</t>
+          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Raste</t>
+          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>offices.kpiMeetings</t>
+          <t>offices.kpiCases</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Средби</t>
+          <t>Случаи</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Takime</t>
+          <t>Raste</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Cases</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>offices.kpiEvents</t>
+          <t>offices.kpiMeetings</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Настани</t>
+          <t>Средби</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ngjarje</t>
+          <t>Takime</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Meetings</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>offices.kpiInitiatives</t>
+          <t>offices.kpiEvents</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Иницијативи</t>
+          <t>Настани</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Iniciativa</t>
+          <t>Ngjarje</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>Events</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>offices.chartByMP</t>
+          <t>offices.kpiInitiatives</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Случаи по пратеник</t>
+          <t>Иницијативи</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Raste sipas deputetit</t>
+          <t>Iniciativa</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cases by MP</t>
+          <t>Initiatives</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>offices.chartByType</t>
+          <t>offices.chartByMP</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Случаи по пратеник</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Raste sipas deputetit</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Cases by MP</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>offices.chartByParty</t>
+          <t>offices.chartByType</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Случаи по партија</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Raste sipas partisë</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cases by party</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>offices.chartByGender</t>
+          <t>offices.chartByParty</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Случаи по пол</t>
+          <t>Случаи по партија</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Raste sipas gjinisë</t>
+          <t>Raste sipas partisë</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cases by gender</t>
+          <t>Cases by party</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>offices.chartByAge</t>
+          <t>offices.chartByGender</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Случаи по возрасна група</t>
+          <t>Случаи по пол</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Raste sipas grupmoshës</t>
+          <t>Raste sipas gjinisë</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cases by age group</t>
+          <t>Cases by gender</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>offices.chartByEthnicity</t>
+          <t>offices.chartByAge</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Случаи по етничка припадност</t>
+          <t>Случаи по возрасна група</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Raste sipas përkatësisë etnike</t>
+          <t>Raste sipas grupmoshës</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cases by ethnicity</t>
+          <t>Cases by age group</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>offices.chartOverTime</t>
+          <t>offices.chartByEthnicity</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Случаи по период</t>
+          <t>Случаи по етничка припадност</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raste sipas periudhës</t>
+          <t>Raste sipas përkatësisë etnike</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cases over time</t>
+          <t>Cases by ethnicity</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>offices.male</t>
+          <t>offices.chartOverTime</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Машки</t>
+          <t>Случаи по период</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Meshkuj</t>
+          <t>Raste sipas periudhës</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Cases over time</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>offices.female</t>
+          <t>offices.male</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Женски</t>
+          <t>Машки</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Femra</t>
+          <t>Meshkuj</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>map.title</t>
+          <t>offices.female</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Локации на канцеларии</t>
+          <t>Женски</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Vendndodhjet e zyrave</t>
+          <t>Femra</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Office locations</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>map.locatedSuffix</t>
+          <t>map.title</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>лоцирани канцеларии на мапата</t>
+          <t>Локации на канцеларии</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>zyra të lokalizuara në hartë</t>
+          <t>Vendndodhjet e zyrave</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>offices located on the map</t>
+          <t>Office locations</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>map.popupTitle</t>
+          <t>map.locatedSuffix</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Канцеларија</t>
+          <t>лоцирани канцеларии на мапата</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>zyra të lokalizuara në hartë</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>offices located on the map</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>profile.title</t>
+          <t>map.popupTitle</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Профил на пратеник</t>
+          <t>Канцеларија</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Profili i deputetit</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MP profile</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>profile.subtitle</t>
+          <t>profile.title</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
+          <t>Профил на пратеник</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
+          <t>Profili i deputetit</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
+          <t>MP profile</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>profile.sectionQuestions</t>
+          <t>profile.subtitle</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Парламентарни прашања</t>
+          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pyetje parlamentare</t>
+          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>profile.sectionActivity</t>
+          <t>profile.sectionQuestions</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Активност во Собранието</t>
+          <t>Парламентарни прашања</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Aktiviteti në Kuvend</t>
+          <t>Pyetje parlamentare</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Activity in the Assembly</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>profile.sectionOffice</t>
+          <t>profile.sectionActivity</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Канцеларија за контакт</t>
+          <t>Активност во Собранието</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Zyra e kontaktit</t>
+          <t>Aktiviteti në Kuvend</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Contact office</t>
+          <t>Activity in the Assembly</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>profile.noOfficeData</t>
+          <t>profile.sectionOffice</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
+          <t>Канцеларија за контакт</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
+          <t>Zyra e kontaktit</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>This MP has no recorded citizen cases.</t>
+          <t>Contact office</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>profile.noQuestionsData</t>
+          <t>profile.noOfficeData</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
+          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
+          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>This MP asked no questions in the current mandate.</t>
+          <t>This MP has no recorded citizen cases.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>profile.questionsAsked</t>
+          <t>profile.noQuestionsData</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>This MP asked no questions in the current mandate.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>profile.plenaryAttendance</t>
+          <t>profile.questionsAsked</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>profile.committees</t>
+          <t>profile.plenaryAttendance</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>profile.citizenCases</t>
+          <t>profile.committees</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Граѓански случаи</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Raste qytetare</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Citizen cases</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>profile.topInstitutions</t>
+          <t>profile.citizenCases</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Најчесто адресирани институции</t>
+          <t>Граѓански случаи</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Institucionet më të adresuara</t>
+          <t>Raste qytetare</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Most frequently addressed institutions</t>
+          <t>Citizen cases</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>profile.recentQuestions</t>
+          <t>profile.topInstitutions</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Последни прашања</t>
+          <t>Најчесто адресирани институции</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Pyetjet e fundit</t>
+          <t>Institucionet më të adresuara</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Recent questions</t>
+          <t>Most frequently addressed institutions</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>profile.casesByType</t>
+          <t>profile.recentQuestions</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Последни прашања</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Pyetjet e fundit</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Recent questions</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>profile.independentBody</t>
+          <t>profile.casesByType</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Независно тело</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Organ i pavarur</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Independent body</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>profile.sort.name</t>
+          <t>profile.independentBody</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Абецеден ред</t>
+          <t>Независно тело</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Rend alfabetik</t>
+          <t>Organ i pavarur</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Alphabetical</t>
+          <t>Independent body</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>profile.sort.composite</t>
+          <t>profile.sort.name</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Општа активност</t>
+          <t>Абецеден ред</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Rend alfabetik</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>Alphabetical</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>profile.sort.questions</t>
+          <t>profile.sort.composite</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Прашања (2024–28)</t>
+          <t>Општа активност</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pyetje (2024–28)</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Questions (2024–28)</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>profile.sort.attendance</t>
+          <t>profile.sort.questions</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Прашања (2024–28)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Pyetje (2024–28)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Questions (2024–28)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>profile.sort.discussions</t>
+          <t>profile.sort.attendance</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>profile.sort.laws</t>
+          <t>profile.sort.discussions</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>profile.sort.amendments</t>
+          <t>profile.sort.laws</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>profile.sort.committees</t>
+          <t>profile.sort.amendments</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>home.pageTitle</t>
+          <t>profile.sort.committees</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Парламентарни отворени податоци</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Të dhëna të hapura parlamentare</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Parliamentary open data</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>home.badge</t>
+          <t>home.pageTitle</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Собрание на Република Северна Македонија · 2024–2028</t>
+          <t>Парламентарни отворени податоци</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
+          <t>Të dhëna të hapura parlamentare</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
+          <t>Parliamentary open data</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>home.heroTitle</t>
+          <t>home.badge</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Интерактивен панел на отворени податоци</t>
+          <t>Собрание на Република Северна Македонија · 2024–2028</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Panel interaktiv i të dhënave të hapura</t>
+          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Interactive open data dashboard</t>
+          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>home.heroSubtitle</t>
+          <t>home.heroTitle</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>на Собранието на Република Северна Македонија</t>
+          <t>Интерактивен панел на отворени податоци</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
+          <t>Panel interaktiv i të dhënave të hapura</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>of the Assembly of the Republic of North Macedonia</t>
+          <t>Interactive open data dashboard</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>home.kpiQuestions</t>
+          <t>home.heroSubtitle</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>на Собранието на Република Северна Македонија</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pyetje deputetësh</t>
+          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>of the Assembly of the Republic of North Macedonia</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>home.kpiQuestionsNote</t>
+          <t>home.kpiQuestions</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>590 одговорени</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>590 të përgjigjura</t>
+          <t>Pyetje deputetësh</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>590 answered</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>home.kpiMPs</t>
+          <t>home.kpiQuestionsNote</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>590 одговорени</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>590 të përgjigjura</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>590 answered</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>home.kpiMPsNote</t>
+          <t>home.kpiMPs</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Активен состав 2024–2028</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Përbërja aktive 2024–2028</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Active assembly 2024–2028</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>home.kpiOffices</t>
+          <t>home.kpiMPsNote</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Канцеларии</t>
+          <t>Активен состав 2024–2028</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>Përbërja aktive 2024–2028</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Offices</t>
+          <t>Active assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>home.kpiOfficesNote</t>
+          <t>home.kpiOffices</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>за контакт со граѓани</t>
+          <t>Канцеларии</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>për kontakt me qytetarët</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>for citizen contact</t>
+          <t>Offices</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>home.descQuestions</t>
+          <t>home.kpiOfficesNote</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
+          <t>за контакт со граѓани</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
+          <t>për kontakt me qytetarët</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
+          <t>for citizen contact</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>home.descMyMP</t>
+          <t>home.descQuestions</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
+          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
+          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
+          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>home.descOffices</t>
+          <t>home.descMyMP</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
+          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
+          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
+          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>home.descProfile</t>
+          <t>home.descOffices</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
+          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
+          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Unified MP profile: parliamentary activity and citizen cases</t>
+          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>home.open</t>
+          <t>home.descProfile</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Отвори</t>
+          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hap</t>
+          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Unified MP profile: parliamentary activity and citizen cases</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>home.disclaimerSupport</t>
+          <t>home.open</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
+          <t>Отвори</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
+          <t>Hap</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPre</t>
+          <t>home.disclaimerSupport</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Контролната табла користи податоци преземени од</t>
+          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Paneli përdor të dhëna të marra nga</t>
+          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>The dashboard uses data sourced from</t>
+          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPost</t>
+          <t>home.disclaimerDataPre</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
+          <t>Контролната табла користи податоци преземени од</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
+          <t>Paneli përdor të dhëna të marra nga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
+          <t>The dashboard uses data sourced from</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>about.p1</t>
+          <t>home.disclaimerDataPost</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
+          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
+          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
+          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>about.p2</t>
+          <t>about.p1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
+          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
+          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
+          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>about.p3</t>
+          <t>about.p2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
+          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
+          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
+          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>about.goalsIntro</t>
+          <t>about.p3</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
+          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
+          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>In pursuing our vision and mission, our long-term goals are:</t>
+          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>about.goals.0</t>
+          <t>about.goalsIntro</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Балансиран социо економски развој</t>
+          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Zhvillim i balancuar socio-ekonomik</t>
+          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Balanced socio-economic development</t>
+          <t>In pursuing our vision and mission, our long-term goals are:</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>about.goals.1</t>
+          <t>about.goals.0</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Активна граѓанска вклученост</t>
+          <t>Балансиран социо економски развој</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Përfshirje aktive qytetare</t>
+          <t>Zhvillim i balancuar socio-ekonomik</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Active civic engagement</t>
+          <t>Balanced socio-economic development</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>about.goals.2</t>
+          <t>about.goals.1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Партиципативна политичка култура</t>
+          <t>Активна граѓанска вклученост</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Kulturë politike participative</t>
+          <t>Përfshirje aktive qytetare</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Participative political culture</t>
+          <t>Active civic engagement</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>about.goals.3</t>
+          <t>about.goals.2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Остварување на либерални вредности во општеството</t>
+          <t>Партиципативна политичка култура</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Realizimi i vlerave liberale në shoqëri</t>
+          <t>Kulturë politike participative</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Realising liberal values in society</t>
+          <t>Participative political culture</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>about.goals.4</t>
+          <t>about.goals.3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Почит кон владеење на правото и доброто владеење</t>
+          <t>Остварување на либерални вредности во општеството</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
+          <t>Realizimi i vlerave liberale në shoqëri</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Respect for the rule of law and good governance</t>
+          <t>Realising liberal values in society</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>about.goals.5</t>
+          <t>about.goals.4</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Промоција на одржливо образование</t>
+          <t>Почит кон владеење на правото и доброто владеење</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Promovimi i arsimit të qëndrueshëm</t>
+          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Promotion of sustainable education</t>
+          <t>Respect for the rule of law and good governance</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>about.goals.6</t>
+          <t>about.goals.5</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
+          <t>Промоција на одржливо образование</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Realizimi i një procesi vendimmarrjeje të bazuar në dëshmi</t>
+          <t>Promovimi i arsimit të qëndrueshëm</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Achieving an evidence-based decision-making process</t>
+          <t>Promotion of sustainable education</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>about.goals.7</t>
+          <t>about.goals.6</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Мултиетничко и мултикултурно сопостоење</t>
+          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bashkëjetesë multietnike dhe multikulturore</t>
+          <t>Realizimi i një procesi të vendimmarrjes së bazuar në dëshmi</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Multi-ethnic and multicultural coexistence</t>
+          <t>Achieving an evidence-based decision-making process</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>project.p1</t>
+          <t>about.goals.7</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
+          <t>Мултиетничко и мултикултурно сопостоење</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
+          <t>Bashkëjetesë multietnike dhe multikulturore</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
+          <t>Multi-ethnic and multicultural coexistence</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>project.p2</t>
+          <t>project.p1</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
+          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
+          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
+          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>project.p3</t>
+          <t>project.p2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
+          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
+          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
+          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>methodology.title</t>
+          <t>project.p3</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Методологија</t>
+          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Metodologjia</t>
+          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>methodology.subtitle</t>
+          <t>methodology.title</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Извори, ограничувања и процес на освежување</t>
+          <t>Методологија</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
+          <t>Metodologjia</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Sources, limitations and the update process</t>
+          <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>methodology.formatLabel</t>
+          <t>methodology.subtitle</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Формат</t>
+          <t>Извори, ограничувања и процес на освежување</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Formati</t>
+          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Sources, limitations and the update process</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>methodology.recordsLabel</t>
+          <t>methodology.formatLabel</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>записи</t>
+          <t>Формат</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>regjistrime</t>
+          <t>Formati</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>records</t>
+          <t>Format</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>methodology.lastPortalUpdate</t>
+          <t>methodology.recordsLabel</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Последно освежување на порталот</t>
+          <t>записи</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Përditësimi i fundit i portalit</t>
+          <t>regjistrime</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Last portal update</t>
+          <t>records</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>methodology.sources.0.name</t>
+          <t>methodology.lastPortalUpdate</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Пратенички прашања 2024–2028</t>
+          <t>Последно освежување на порталот</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve 2024–2028</t>
+          <t>Përditësimi i fundit i portalit</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Parliamentary questions 2024–2028</t>
+          <t>Last portal update</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.0</t>
+          <t>methodology.sources.0.name</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
+          <t>Пратенички прашања 2024–2028</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
+          <t>Pyetjet e deputetëve 2024–2028</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
+          <t>Parliamentary questions 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.1</t>
+          <t>methodology.sources.0.notes.0</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
+          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
+          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
+          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.2</t>
+          <t>methodology.sources.0.notes.1</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
+          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
+          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>91 records have no assigned institution — addressed to independent bodies.</t>
+          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.3</t>
+          <t>methodology.sources.0.notes.2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
+          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
+          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
+          <t>91 records have no assigned institution — addressed to independent bodies.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>methodology.sources.1.name</t>
+          <t>methodology.sources.0.notes.3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
+          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
+          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
+          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.0</t>
+          <t>methodology.sources.1.name</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
+          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
+          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Periodic report, not updated since November 2025.</t>
+          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.1</t>
+          <t>methodology.sources.1.notes.0</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
+          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
+          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>The XLSX file uses a three-row header structure with internal codes.</t>
+          <t>Periodic report, not updated since November 2025.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.2</t>
+          <t>methodology.sources.1.notes.1</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
+          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
+          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
+          <t>The XLSX file uses a three-row header structure with internal codes.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>methodology.sources.2.name</t>
+          <t>methodology.sources.1.notes.2</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.0</t>
+          <t>methodology.sources.2.name</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.1</t>
+          <t>methodology.sources.2.notes.0</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
+          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
+          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Format: tidy/long — each category is a separate row.</t>
+          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.2</t>
+          <t>methodology.sources.2.notes.1</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
+          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
+          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>The UUID identifier is used to join with the other datasets.</t>
+          <t>Format: tidy/long — each category is a separate row.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyTitle</t>
+          <t>methodology.sources.2.notes.2</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Активен состав (120 пратеници)</t>
+          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Përbërja aktive (120 deputetë)</t>
+          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Active assembly (120 MPs)</t>
+          <t>The UUID identifier is used to join with the other datasets.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP1</t>
+          <t>methodology.activeAssemblyTitle</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
+          <t>Активен состав (120 пратеници)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
+          <t>Përbërja aktive (120 deputetë)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
+          <t>Active assembly (120 MPs)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP2</t>
+          <t>methodology.activeAssemblyP1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
+          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
+          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
+          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>methodology.joinTitle</t>
+          <t>methodology.activeAssemblyP2</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Поврзување на датасети</t>
+          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Lidhja e dataseteve</t>
+          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Joining the datasets</t>
+          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>methodology.joinP1</t>
+          <t>methodology.joinTitle</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
+          <t>Поврзување на датасети</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
+          <t>Lidhja e dataseteve</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
+          <t>Joining the datasets</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>methodology.joinP2</t>
+          <t>methodology.joinP1</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
+          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
+          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
+          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>methodology.refreshTitle</t>
+          <t>methodology.joinP2</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Процес на освежување</t>
+          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Procesi i përditësimit</t>
+          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Update process</t>
+          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>methodology.refreshIntro</t>
+          <t>methodology.refreshTitle</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
+          <t>Процес на освежување</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
+          <t>Procesi i përditësimit</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
+          <t>Update process</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1pre</t>
+          <t>methodology.refreshIntro</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Skripti</t>
+          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1post</t>
+          <t>methodology.refreshStep1pre</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ги презема новите датотеки од CKAN API.</t>
+          <t>Скриптата</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>i merr skedarët e rinj nga CKAN API.</t>
+          <t>Skripta</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>fetches the new files from the CKAN API.</t>
+          <t>The script</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2pre</t>
+          <t>methodology.refreshStep1post</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>ги презема новите датотеки од CKAN API.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Skripti</t>
+          <t>i merr skedarët e rinj nga CKAN API.</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>fetches the new files from the CKAN API.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2post</t>
+          <t>methodology.refreshStep2pre</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ги обработува и генерира чисти JSON датотеки.</t>
+          <t>Скриптата</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>i përpunon dhe gjeneron skedarë JSON të pastër.</t>
+          <t>Skripta</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>processes them and generates clean JSON files.</t>
+          <t>The script</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>methodology.refreshStep3</t>
+          <t>methodology.refreshStep2post</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+          <t>ги обработува и генерира чисти JSON датотеки.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The system automatically rebuilds and deploys the dashboard.</t>
+          <t>processes them and generates clean JSON files.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
+          <t>methodology.refreshStep3</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>The system automatically rebuilds and deploys the dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>methodology.lastProcessedLabel</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Dashboard последно обработен:</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>Paneli i përpunuar së fundi:</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Dashboard last processed:</t>
         </is>
@@ -5576,7 +5594,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Partia e Re Socialdemokrate</t>
+          <t>Partia e Re Social-demokrate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5906,7 +5924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lupço Nikollovski</t>
+          <t>Ljupço Nikollovski</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5923,7 +5941,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lupço Prendzov</t>
+          <t>Ljupço Prenxhov</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5991,7 +6009,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aleksandra Nikolovska</t>
+          <t>Aleksandra Nikollovska</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6059,7 +6077,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Antonio Miloshoski</t>
+          <t>Antonio Milloshoski</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6110,7 +6128,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Беким Ќоку</t>
+          <t>Bekim Qoku</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6161,7 +6179,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biserka Zlateska</t>
+          <t>Biserka Zllateska</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6195,7 +6213,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blagica Lasovska</t>
+          <t>Bllagica Llasovska</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6212,7 +6230,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blagoj Boçvarski</t>
+          <t>Bllagoj Boçvarski</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6263,7 +6281,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Borislav Krmov</t>
+          <t>Borisllav Krmov</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6331,7 +6349,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Valentina Marchevska</t>
+          <t>Valentina Marçevska</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6399,7 +6417,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vesna Gjorgieva</t>
+          <t>Vesna Gjorgjieva</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6467,7 +6485,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Daniel Stojçevski</t>
+          <t>Daniell Stojçevski</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6484,7 +6502,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daniela Belimova</t>
+          <t>Daniella Belimova</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6501,7 +6519,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Daniela Nikollova</t>
+          <t>Daniella Nikollova</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6518,7 +6536,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Daniela Hristova</t>
+          <t>Daniella Hristova</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6637,7 +6655,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dragan Nedeljkoviq</t>
+          <t>Dragan Nedelkoviq</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6688,7 +6706,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dusko Ivanov</t>
+          <t>Dushko Ivanov</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6739,7 +6757,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Emil Spasovski</t>
+          <t>Emill Spasovski</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6756,7 +6774,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Emilija Angelova</t>
+          <t>Emilija Angellova</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6807,7 +6825,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Зеќирја Таири</t>
+          <t>Zeqirja Tairi</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6824,7 +6842,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Zijadin Sela</t>
+          <t>Ziadin Sela</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6841,7 +6859,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zlatko Penkov</t>
+          <t>Zllatko Penkov</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7113,7 +7131,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marija Petruševska</t>
+          <t>Marija Petrushevska</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7164,7 +7182,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Menduh Taçi</t>
+          <t>Menduh Thaçi</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7181,7 +7199,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Merita Kolçi Kodxhaxhiku</t>
+          <t>Merita Kolçi Koxhaxhiku</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7385,7 +7403,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Olga Lozanovska</t>
+          <t>Ollga Llozanovska</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7487,7 +7505,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rashela Mizrahi</t>
+          <t>Rashella Mizrahi</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7657,7 +7675,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sanja Lukarevska</t>
+          <t>Sanja Llukarevska</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7691,7 +7709,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Silvana Angellovska</t>
+          <t>Sillvana Angellovska</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7725,7 +7743,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Slavjanka Petrovska</t>
+          <t>Sllavjanka Petrovska</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7793,7 +7811,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fatmir Bytyçi</t>
+          <t>Fatmir Bytqi</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7810,7 +7828,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Feride Hadjiu</t>
+          <t>Feride Haxhiu</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8358,7 +8376,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transporti dhe infrastruktura</t>
+          <t>Transport dhe infrastrukturë</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8392,7 +8410,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shërbimet sociale</t>
+          <t>Shërbime sociale</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8409,7 +8427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ndihma juridike</t>
+          <t>Ndihmë juridike</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8443,7 +8461,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arsimi</t>
+          <t>Arsim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8460,7 +8478,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nismat për zhvillimin e bashkësisë</t>
+          <t>Nismat për zhvillimin e komunës</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8477,7 +8495,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qasja në shërbimet publike</t>
+          <t>Qasja në shërbime publike</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/translations.xlsx
+++ b/translations.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D213"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4418,702 +4418,724 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>methodology.title</t>
+          <t>project.p4</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Методологија</t>
+          <t>Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество е поддржан преку грантовата шема Digital Spark, како дел од проектот Regional Support Mechanism EECA, спроведуван од Фондацијата Метаморфозис и TechSoup, во партнерство со CIVICUS и во рамки на Digital Democracy Initiative (DDI), која го опфаќа Глобалниот југ.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Metodologjia</t>
+          <t>Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare mbështetet përmes skemës së granteve Digital Spark, si pjesë e projektit Regional Support Mechanism EECA, i zbatuar nga Fondacioni Metamorphosis dhe TechSoup, në partneritet me CIVICUS dhe në kuadër të Digital Democracy Initiative (DDI), e cila mbulon Jugun Global.</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Assembly Open Data in Practice: Encouraging Citizen Participation, is supported through the Digital Spark granting scheme, as part of the Regional Support Mechanism EECA project, implemented by Metamorphosis Foundation and TechSoup, in partnership with CIVICUS and under the Digital Democracy Initiative (DDI) that covers the Global South.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>methodology.subtitle</t>
+          <t>methodology.title</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Извори, ограничувања и процес на освежување</t>
+          <t>Методологија</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
+          <t>Metodologjia</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Sources, limitations and the update process</t>
+          <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>methodology.formatLabel</t>
+          <t>methodology.subtitle</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Формат</t>
+          <t>Извори, ограничувања и процес на освежување</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Formati</t>
+          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Sources, limitations and the update process</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>methodology.recordsLabel</t>
+          <t>methodology.formatLabel</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>записи</t>
+          <t>Формат</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>regjistrime</t>
+          <t>Formati</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>records</t>
+          <t>Format</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>methodology.lastPortalUpdate</t>
+          <t>methodology.recordsLabel</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Последно освежување на порталот</t>
+          <t>записи</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Përditësimi i fundit i portalit</t>
+          <t>regjistrime</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Last portal update</t>
+          <t>records</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>methodology.sources.0.name</t>
+          <t>methodology.lastPortalUpdate</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Пратенички прашања 2024–2028</t>
+          <t>Последно освежување на порталот</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve 2024–2028</t>
+          <t>Përditësimi i fundit i portalit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Parliamentary questions 2024–2028</t>
+          <t>Last portal update</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.0</t>
+          <t>methodology.sources.0.name</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
+          <t>Пратенички прашања 2024–2028</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
+          <t>Pyetjet e deputetëve 2024–2028</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
+          <t>Parliamentary questions 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.1</t>
+          <t>methodology.sources.0.notes.0</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
+          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
+          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
+          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.2</t>
+          <t>methodology.sources.0.notes.1</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
+          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
+          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>91 records have no assigned institution — addressed to independent bodies.</t>
+          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.3</t>
+          <t>methodology.sources.0.notes.2</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
+          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
+          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
+          <t>91 records have no assigned institution — addressed to independent bodies.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>methodology.sources.1.name</t>
+          <t>methodology.sources.0.notes.3</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
+          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
+          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
+          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.0</t>
+          <t>methodology.sources.1.name</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
+          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
+          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Periodic report, not updated since November 2025.</t>
+          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.1</t>
+          <t>methodology.sources.1.notes.0</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
+          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
+          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>The XLSX file uses a three-row header structure with internal codes.</t>
+          <t>Periodic report, not updated since November 2025.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.2</t>
+          <t>methodology.sources.1.notes.1</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
+          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
+          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
+          <t>The XLSX file uses a three-row header structure with internal codes.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>methodology.sources.2.name</t>
+          <t>methodology.sources.1.notes.2</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.0</t>
+          <t>methodology.sources.2.name</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.1</t>
+          <t>methodology.sources.2.notes.0</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
+          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
+          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Format: tidy/long — each category is a separate row.</t>
+          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.2</t>
+          <t>methodology.sources.2.notes.1</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
+          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
+          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>The UUID identifier is used to join with the other datasets.</t>
+          <t>Format: tidy/long — each category is a separate row.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyTitle</t>
+          <t>methodology.sources.2.notes.2</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Активен состав (120 пратеници)</t>
+          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Përbërja aktive (120 deputetë)</t>
+          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Active assembly (120 MPs)</t>
+          <t>The UUID identifier is used to join with the other datasets.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP1</t>
+          <t>methodology.activeAssemblyTitle</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
+          <t>Активен состав (120 пратеници)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
+          <t>Përbërja aktive (120 deputetë)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
+          <t>Active assembly (120 MPs)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP2</t>
+          <t>methodology.activeAssemblyP1</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
+          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
+          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
+          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>methodology.joinTitle</t>
+          <t>methodology.activeAssemblyP2</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Поврзување на датасети</t>
+          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Lidhja e dataseteve</t>
+          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Joining the datasets</t>
+          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>methodology.joinP1</t>
+          <t>methodology.joinTitle</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
+          <t>Поврзување на датасети</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
+          <t>Lidhja e dataseteve</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
+          <t>Joining the datasets</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>methodology.joinP2</t>
+          <t>methodology.joinP1</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
+          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
+          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
+          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>methodology.refreshTitle</t>
+          <t>methodology.joinP2</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Процес на освежување</t>
+          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Procesi i përditësimit</t>
+          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Update process</t>
+          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>methodology.refreshIntro</t>
+          <t>methodology.refreshTitle</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
+          <t>Процес на освежување</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
+          <t>Procesi i përditësimit</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
+          <t>Update process</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1pre</t>
+          <t>methodology.refreshIntro</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1post</t>
+          <t>methodology.refreshStep1pre</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ги презема новите датотеки од CKAN API.</t>
+          <t>Скриптата</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>i merr skedarët e rinj nga CKAN API.</t>
+          <t>Skripta</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>fetches the new files from the CKAN API.</t>
+          <t>The script</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2pre</t>
+          <t>methodology.refreshStep1post</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>ги презема новите датотеки од CKAN API.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>i merr skedarët e rinj nga CKAN API.</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>fetches the new files from the CKAN API.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2post</t>
+          <t>methodology.refreshStep2pre</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ги обработува и генерира чисти JSON датотеки.</t>
+          <t>Скриптата</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
+          <t>Skripta</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>processes them and generates clean JSON files.</t>
+          <t>The script</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>methodology.refreshStep3</t>
+          <t>methodology.refreshStep2post</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+          <t>ги обработува и генерира чисти JSON датотеки.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>The system automatically rebuilds and deploys the dashboard.</t>
+          <t>processes them and generates clean JSON files.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>methodology.refreshStep3</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>The system automatically rebuilds and deploys the dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>methodology.lastProcessedLabel</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Dashboard последно обработен:</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>Paneli i përpunuar së fundi:</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>Dashboard last processed:</t>
         </is>

--- a/translations.xlsx
+++ b/translations.xlsx
@@ -12,7 +12,8 @@
     <sheet name="MP names" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Institutions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Case types" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Questions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ethnicities" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Questions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -462,4680 +463,4790 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nav.questions</t>
+          <t>meta.siteName</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>Отворени податоци на Собранието</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve</t>
+          <t>Të dhënat e hapura të Kuvendit</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Assembly Open Data</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nav.mymp</t>
+          <t>meta.description</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Активност на пратеник</t>
+          <t>Јавен интерактивен приказ на отворените податоци на Собранието — пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetit</t>
+          <t>Paraqitje interaktive publike e të dhënave të hapura të Kuvendit — pyetjet e deputetëve, platforma „Deputeti im“ dhe zyrat e kontaktit me qytetarët.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MP activity</t>
+          <t>A public interactive dashboard of the Assembly's open data — parliamentary questions, the “My MP” platform and the citizen contact offices.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nav.offices</t>
+          <t>nav.questions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit</t>
+          <t>Pyetjet e deputetëve</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Contact offices</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nav.profile</t>
+          <t>nav.mymp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Профил на пратеник</t>
+          <t>Активност на пратеник</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Profili i deputetit</t>
+          <t>Aktiviteti i deputetit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MP profile</t>
+          <t>MP activity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nav.methodology</t>
+          <t>nav.offices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Методологија</t>
+          <t>Канцеларии за контакт</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Metodologjia</t>
+          <t>Zyrat e kontaktit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Contact offices</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nav.project</t>
+          <t>nav.profile</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>За проектот</t>
+          <t>Профил на пратеник</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rreth projektit</t>
+          <t>Profili i deputetit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>About the project</t>
+          <t>MP profile</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nav.about</t>
+          <t>nav.methodology</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>За ИДСЦС</t>
+          <t>Методологија</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rreth IDSCS</t>
+          <t>Metodologjia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>About IDSCS</t>
+          <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nav.home</t>
+          <t>nav.project</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Почетна</t>
+          <t>За проектот</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ballina</t>
+          <t>Rreth projektit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>About the project</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nav.language</t>
+          <t>nav.about</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Јазик</t>
+          <t>За ИДСЦС</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gjuha</t>
+          <t>Rreth IDSCS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>About IDSCS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>common.filterByMP</t>
+          <t>nav.home</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Избери пратеник</t>
+          <t>Почетна</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zgjidhni deputetin</t>
+          <t>Ballina</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Select MP</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>common.filterByParty</t>
+          <t>nav.language</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Избери партија</t>
+          <t>Јазик</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zgjidhni partinë</t>
+          <t>Gjuha</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Select party</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>common.filterByInstitution</t>
+          <t>common.filterByMP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Избери институција</t>
+          <t>Избери пратеник</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zgjidhni institucionin</t>
+          <t>Zgjidhni deputetin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Select institution</t>
+          <t>Select MP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>common.filterByStatus</t>
+          <t>common.filterByParty</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Избери статус</t>
+          <t>Избери партија</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zgjidhni statusin</t>
+          <t>Zgjidhni partinë</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Select status</t>
+          <t>Select party</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>common.filterByPeriod</t>
+          <t>common.filterByInstitution</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Избери период</t>
+          <t>Избери институција</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zgjidhni periudhën</t>
+          <t>Zgjidhni institucionin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Select period</t>
+          <t>Select institution</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>common.search</t>
+          <t>common.filterByStatus</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Пребарај</t>
+          <t>Избери статус</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kërko</t>
+          <t>Zgjidhni statusin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Select status</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>common.download</t>
+          <t>common.filterByPeriod</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Преземи</t>
+          <t>Избери период</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shkarko</t>
+          <t>Zgjidhni periudhën</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Select period</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>common.downloadCSV</t>
+          <t>common.search</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Преземи податоци (CSV)</t>
+          <t>Пребарај</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shkarko të dhënat (CSV)</t>
+          <t>Kërko</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Download data (CSV)</t>
+          <t>Search</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>common.downloadPNG</t>
+          <t>common.download</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Преземи слика (PNG)</t>
+          <t>Преземи</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shkarko imazhin (PNG)</t>
+          <t>Shkarko</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Download image (PNG)</t>
+          <t>Download</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>common.downloadJSON</t>
+          <t>common.downloadCSV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Преземи JSON</t>
+          <t>Преземи податоци (CSV)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shkarko JSON</t>
+          <t>Shkarko të dhënat (CSV)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Download JSON</t>
+          <t>Download data (CSV)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>common.lastUpdated</t>
+          <t>common.downloadPNG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Последно освежување</t>
+          <t>Преземи слика (PNG)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Përditësimi i fundit</t>
+          <t>Shkarko imazhin (PNG)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Last updated</t>
+          <t>Download image (PNG)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>common.noData</t>
+          <t>common.downloadJSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Нема податоци</t>
+          <t>Преземи JSON</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nuk ka të dhëna</t>
+          <t>Shkarko JSON</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>Download JSON</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>common.allMPs</t>
+          <t>common.lastUpdated</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Сите пратеници</t>
+          <t>Последно освежување</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Të gjithë deputetët</t>
+          <t>Përditësimi i fundit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>All MPs</t>
+          <t>Last updated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>common.allParties</t>
+          <t>common.noData</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Сите партии</t>
+          <t>Нема податоци</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Të gjitha partitë</t>
+          <t>Nuk ka të dhëna</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>All parties</t>
+          <t>No data</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>common.total</t>
+          <t>common.allMPs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Вкупно</t>
+          <t>Сите пратеници</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gjithsej</t>
+          <t>Të gjithë deputetët</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>All MPs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>common.showAll</t>
+          <t>common.allParties</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Прикажи ги сите</t>
+          <t>Сите партии</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shfaq të gjithë</t>
+          <t>Të gjitha partitë</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Show all</t>
+          <t>All parties</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>common.showLess</t>
+          <t>common.total</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Прикажи помалку</t>
+          <t>Вкупно</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shfaq më pak</t>
+          <t>Gjithsej</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Show less</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>common.of</t>
+          <t>common.showAll</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>од</t>
+          <t>Прикажи ги сите</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nga</t>
+          <t>Shfaq të gjithë</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>Show all</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>common.answered</t>
+          <t>common.showLess</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Одговорено</t>
+          <t>Прикажи помалку</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Përgjigjur</t>
+          <t>Shfaq më pak</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Answered</t>
+          <t>Show less</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>common.pending</t>
+          <t>common.of</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Доставено</t>
+          <t>од</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dërguar</t>
+          <t>nga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>of</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>common.sessions</t>
+          <t>common.answered</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Седници</t>
+          <t>Одговорено</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seanca</t>
+          <t>Përgjigjur</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>Answered</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>common.source</t>
+          <t>common.pending</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Извор</t>
+          <t>Доставено</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Burimi</t>
+          <t>Dërguar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>common.party</t>
+          <t>common.sessions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Партија</t>
+          <t>Седници</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Partia</t>
+          <t>Seanca</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Party</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>common.category</t>
+          <t>common.source</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Категорија</t>
+          <t>Извор</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kategoria</t>
+          <t>Burimi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>common.subcategory</t>
+          <t>common.party</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Подкатегорија</t>
+          <t>Партија</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nënkategoria</t>
+          <t>Partia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Party</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>common.filter</t>
+          <t>common.category</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Филтер</t>
+          <t>Категорија</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Filtër</t>
+          <t>Kategoria</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>common.sortBy</t>
+          <t>common.subcategory</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Сортирај по</t>
+          <t>Подкатегорија</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rendit sipas</t>
+          <t>Nënkategoria</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sort by</t>
+          <t>Subcategory</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>common.results</t>
+          <t>common.filter</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>резултати</t>
+          <t>Филтер</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>rezultate</t>
+          <t>Filtër</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>Filter</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>common.close</t>
+          <t>common.sortBy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Затвори</t>
+          <t>Сортирај по</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mbyll</t>
+          <t>Rendit sipas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Sort by</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>common.prev</t>
+          <t>common.results</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Претходни</t>
+          <t>резултати</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Të mëparshme</t>
+          <t>rezultate</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Previous</t>
+          <t>results</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>common.next</t>
+          <t>common.close</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Следни</t>
+          <t>Затвори</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Të mëtejshme</t>
+          <t>Mbyll</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>common.mpsLower</t>
+          <t>common.prev</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>пратеници</t>
+          <t>Претходни</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>deputetë</t>
+          <t>Të mëparshme</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>Previous</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>common.skipToContent</t>
+          <t>common.next</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Прескокни на содржината</t>
+          <t>Следни</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kalo te përmbajtja</t>
+          <t>Të mëtejshme</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Skip to content</t>
+          <t>Next</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>footer.dataNotePre</t>
+          <t>common.mpsLower</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Податоците се преземени од</t>
+          <t>пратеници</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Të dhënat janë marrë nga</t>
+          <t>deputetë</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Data is sourced from</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>footer.portalName</t>
+          <t>common.skipToContent</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Порталот за отворени податоци на Собранието на Република Северна Македонија</t>
+          <t>Прескокни на содржината</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut</t>
+          <t>Kalo te përmbajtja</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>the Open Data Portal of the Assembly of the Republic of North Macedonia</t>
+          <t>Skip to content</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>footer.dataNotePost</t>
+          <t>footer.dataNotePre</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>, во формата и содржината во која тие се објавени од Собранието.</t>
+          <t>Податоците се преземени од</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
+          <t>Të dhënat janë marrë nga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>, in the form and content in which it is published by the Assembly.</t>
+          <t>Data is sourced from</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>questions.title</t>
+          <t>footer.portalName</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>Порталот за отворени податоци на Собранието на Република Северна Македонија</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve</t>
+          <t>Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>the Open Data Portal of the Assembly of the Republic of North Macedonia</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>questions.subtitle</t>
+          <t>footer.dataNotePost</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Прашања поставени во Собранието 2024–2028</t>
+          <t>, во формата и содржината во која тие се објавени од Собранието.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara në Kuvend 2024–2028</t>
+          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Questions raised in the Assembly 2024–2028</t>
+          <t>, in the form and content in which it is published by the Assembly.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>questions.kpiTotal</t>
+          <t>questions.title</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Вкупно прашања</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gjithsej pyetje</t>
+          <t>Pyetjet e deputetëve</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Total questions</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>questions.kpiAnswered</t>
+          <t>questions.subtitle</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Одговорени</t>
+          <t>Прашања поставени во Собранието 2024–2028</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Të përgjigjura</t>
+          <t>Pyetje të parashtruara në Kuvend 2024–2028</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Answered</t>
+          <t>Questions raised in the Assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>questions.kpiPending</t>
+          <t>questions.kpiTotal</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Во тек</t>
+          <t>Вкупно прашања</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Në pritje</t>
+          <t>Gjithsej pyetje</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Total questions</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>questions.kpiSessions</t>
+          <t>questions.kpiAnswered</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Опфатени седници</t>
+          <t>Одговорени</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seanca të përfshira</t>
+          <t>Të përgjigjura</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sessions covered</t>
+          <t>Answered</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>questions.chartByMP</t>
+          <t>questions.kpiPending</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Прашања по пратеник</t>
+          <t>Во тек</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pyetje sipas deputetit</t>
+          <t>Në pritje</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Questions by MP</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>questions.chartByInstitution</t>
+          <t>questions.kpiSessions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Прашања по институција</t>
+          <t>Опфатени седници</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pyetje sipas institucionit</t>
+          <t>Seanca të përfshira</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Questions by institution</t>
+          <t>Sessions covered</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>questions.chartAnsweredVsPending</t>
+          <t>questions.chartByMP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Одговорени наспроти во тек — по институција</t>
+          <t>Прашања по пратеник</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Të përgjigjura kundrejt në pritje — sipas institucionit</t>
+          <t>Pyetje sipas deputetit</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Answered vs. pending — by institution</t>
+          <t>Questions by MP</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>questions.chartAnswerRate</t>
+          <t>questions.chartByInstitution</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Стапка на одговарање по институција</t>
+          <t>Прашања по институција</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shkalla e përgjigjes sipas institucionit</t>
+          <t>Pyetje sipas institucionit</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Answer rate by institution</t>
+          <t>Questions by institution</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>questions.chartAnswerRateNote</t>
+          <t>questions.chartAnsweredVsPending</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Сортирани по најмала стапка — кои институции ги одложуваат одговорите</t>
+          <t>Одговорени наспроти во тек — по институција</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Të renditura sipas shkallës më të ulët — cilat institucione vonojnë përgjigjet</t>
+          <t>Të përgjigjura kundrejt në pritje — sipas institucionit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sorted by lowest rate — which institutions delay their answers</t>
+          <t>Answered vs. pending — by institution</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>questions.chartByParty</t>
+          <t>questions.chartAnswerRate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Прашања по партија</t>
+          <t>Стапка на одговарање по институција</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pyetje sipas grupit parlamentar</t>
+          <t>Shkalla e përgjigjes sipas institucionit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Questions by party</t>
+          <t>Answer rate by institution</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>questions.chartByPartyNote</t>
+          <t>questions.chartAnswerRateNote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Вкупно прашања по партија, со стапка на одговарање</t>
+          <t>Сортирани по најмала стапка — кои институции ги одложуваат одговорите</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gjithsej pyetje sipas partisë, me shkallën e përgjigjes</t>
+          <t>Të renditura sipas shkallës më të ulët — cilat institucione vonojnë përgjigjet</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Total questions by party, with answer rate</t>
+          <t>Sorted by lowest rate — which institutions delay their answers</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>questions.chartTimeline</t>
+          <t>questions.chartByParty</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Прашања по седница</t>
+          <t>Прашања по партија</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pyetje sipas seancës</t>
+          <t>Pyetje sipas grupit parlamentar</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Questions by session</t>
+          <t>Questions by party</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>questions.sessionFull</t>
+          <t>questions.chartByPartyNote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Седница бр.</t>
+          <t>Вкупно прашања по партија, со стапка на одговарање</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seanca nr.</t>
+          <t>Gjithsej pyetje sipas partisë, me shkallën e përgjigjes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Session no.</t>
+          <t>Total questions by party, with answer rate</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>questions.questionsShort</t>
+          <t>questions.chartTimeline</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>прашања</t>
+          <t>Прашања по седница</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>pyetje</t>
+          <t>Pyetje sipas seancës</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Questions by session</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>questions.tableQuestion</t>
+          <t>questions.sessionFull</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Прашање</t>
+          <t>Седница бр.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pyetje</t>
+          <t>Seanca nr.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Session no.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>questions.tableFrom</t>
+          <t>questions.questionsShort</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Пратеник</t>
+          <t>прашања</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Deputeti</t>
+          <t>pyetje</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>questions</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>questions.tableTo</t>
+          <t>questions.tableQuestion</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Институција</t>
+          <t>Прашање</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Institucioni</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Institution</t>
+          <t>Question</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>questions.tableDate</t>
+          <t>questions.tableFrom</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Датум</t>
+          <t>Пратеник</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Deputeti</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>questions.tableStatus</t>
+          <t>questions.tableTo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Институција</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Statusi</t>
+          <t>Institucioni</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Institution</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>questions.detailTitle</t>
+          <t>questions.tableDate</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Детали за прашањето</t>
+          <t>Датум</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Detajet e pyetjes</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Question details</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>questions.detailQuestion</t>
+          <t>questions.tableStatus</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Прашање</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pyetja</t>
+          <t>Statusi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>questions.detailAnswer</t>
+          <t>questions.detailTitle</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Одговор</t>
+          <t>Детали за прашањето</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Përgjigja</t>
+          <t>Detajet e pyetjes</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question details</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>questions.detailNoAnswer</t>
+          <t>questions.detailQuestion</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Одговорот сè уште не е доставен.</t>
+          <t>Прашање</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Përgjigja ende nuk është dorëzuar.</t>
+          <t>Pyetja</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>The answer has not been submitted yet.</t>
+          <t>Question</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>questions.detailNoAnswerSource</t>
+          <t>questions.detailAnswer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Забелешка: Во изворните податоци објавени од Собранието, ова пратеничко прашање е означено како одговорено, но во полето предвидено за одговор повторно е ставен текстот на самото прашање.</t>
+          <t>Одговор</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shënim: Në të dhënat burimore të publikuara nga Kuvendi, kjo pyetje parlamentare është shënuar si e përgjigjur, por në fushën e parashikuar për përgjigje është vendosur përsëri teksti i vetë pyetjes.</t>
+          <t>Përgjigja</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Note: In the source data published by the Assembly, this parliamentary question is marked as answered, but the field intended for the answer again contains the text of the question itself.</t>
+          <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>questions.nullInstitution</t>
+          <t>questions.detailNoAnswer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Независно тело</t>
+          <t>Одговорот сè уште не е доставен.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Organ i pavarur</t>
+          <t>Përgjigja ende nuk është dorëzuar.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Independent body</t>
+          <t>The answer has not been submitted yet.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>questions.nullDate</t>
+          <t>questions.detailNoAnswerSource</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Датумот не е назначен</t>
+          <t>Забелешка: Во изворните податоци објавени од Собранието, ова пратеничко прашање е означено како одговорено, но во полето предвидено за одговор повторно е ставен текстот на самото прашање.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Data nuk është caktuar</t>
+          <t>Shënim: Në të dhënat burimore të publikuara nga Kuvendi, kjo pyetje parlamentare është shënuar si e përgjigjur, por në fushën e parashikuar për përgjigje është vendosur përsëri teksti i vetë pyetjes.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Date not assigned</t>
+          <t>Note: In the source data published by the Assembly, this parliamentary question is marked as answered, but the field intended for the answer again contains the text of the question itself.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>questions.openDetailAria</t>
+          <t>questions.nullInstitution</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Отвори детали за прашање од</t>
+          <t>Независно тело</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hap detajet e pyetjes nga</t>
+          <t>Organ i pavarur</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Open question details from</t>
+          <t>Independent body</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>questions.session</t>
+          <t>questions.nullDate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Седница</t>
+          <t>Датумот не е назначен</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seanca</t>
+          <t>Data nuk është caktuar</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Date not assigned</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>questions.autoTranslated</t>
+          <t>questions.openDetailAria</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Автоматски превод</t>
+          <t>Отвори детали за прашање од</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Përkthim automatik</t>
+          <t>Hap detajet e pyetjes nga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Machine-translated</t>
+          <t>Open question details from</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>questions.aiTranslationNotice</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>questions.session</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Седница</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Përkthimi në gjuhën shqipe i pyetjeve parlamentare është përgatitur me ndihmën e mjeteve të inteligjencës artificiale (AI), duke u bazuar në materialet e disponueshme në gjuhën maqedonase në Portalin e të Dhënave të Hapura të Kuvendit. Deri në ditën e publikimit, materialet në portal ishin të disponueshme vetëm në gjuhën maqedonase.</t>
+          <t>Seanca</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The English translation of the parliamentary questions was prepared using artificial intelligence (AI) tools, based on the materials available in Macedonian on the Assembly Open Data Portal. As of the date of publication, the materials on the portal were available only in Macedonian.</t>
+          <t>Session</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mymp.title</t>
+          <t>questions.autoTranslated</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Активност на пратеник</t>
+          <t>Автоматски превод</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetit</t>
+          <t>Përkthim automatik</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MP activity</t>
+          <t>Machine-translated</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mymp.subtitle</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
-        </is>
-      </c>
+          <t>questions.aiTranslationNotice</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
+          <t>Përkthimi në gjuhën shqipe i pyetjeve parlamentare është përgatitur me ndihmën e mjeteve të inteligjencës artificiale (AI), duke u bazuar në materialet e disponueshme në gjuhën maqedonase në Portalin e të Dhënave të Hapura të Kuvendit. Deri në ditën e publikimit, materialet në portal ishin të disponueshme vetëm në gjuhën maqedonase.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MP activity for the period January–June 2025</t>
+          <t>The English translation of the parliamentary questions was prepared using artificial intelligence (AI) tools, based on the materials available in Macedonian on the Assembly Open Data Portal. As of the date of publication, the materials on the portal were available only in Macedonian.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mymp.stalenessNote</t>
+          <t>mymp.title</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
+          <t>Активност на пратеник</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
+          <t>Aktiviteti i deputetit</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
+          <t>MP activity</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mymp.mostActiveTitle</t>
+          <t>mymp.subtitle</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Најактивен пратеник</t>
+          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Deputeti më aktiv</t>
+          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Most active MP</t>
+          <t>MP activity for the period January–June 2025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mymp.mostActiveNote</t>
+          <t>mymp.stalenessNote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
+          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
+          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
+          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mymp.kpiMPs</t>
+          <t>mymp.mostActiveTitle</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>Најактивен пратеник</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>Deputeti më aktiv</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>Most active MP</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mymp.newlySeatedNote</t>
+          <t>mymp.mostActiveNote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>стапиле на должност по периодот на извештајот</t>
+          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>kanë marrë mandatin pas periudhës së raportit</t>
+          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>took office after the reporting period</t>
+          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mymp.noPeriodData</t>
+          <t>mymp.kpiMPs</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Стапил на должност по последниот извештај за активност</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Took office after the latest activity report</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mymp.kpiAvgAttendance</t>
+          <t>mymp.newlySeatedNote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Просечно присуство</t>
+          <t>стапиле на должност по периодот на извештајот</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Prezenca mesatare</t>
+          <t>kanë marrë mandatin pas periudhës së raportit</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Average attendance</t>
+          <t>took office after the reporting period</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mymp.kpiZeroQuestions</t>
+          <t>mymp.noPeriodData</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Пратеници без прашања</t>
+          <t>Стапил на должност по последниот извештај за активност</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Deputetë pa pyetje</t>
+          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MPs with no questions</t>
+          <t>Took office after the latest activity report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mymp.chartAttendance</t>
+          <t>mymp.kpiAvgAttendance</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Просечно присуство</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Prezenca mesatare</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>Average attendance</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mymp.chartDiscussions</t>
+          <t>mymp.kpiZeroQuestions</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Пратеници без прашања</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Deputetë pa pyetje</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>MPs with no questions</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mymp.chartQuestions</t>
+          <t>mymp.chartAttendance</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mymp.colMP</t>
+          <t>mymp.chartDiscussions</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Пратеник</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Deputeti</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mymp.colAttendance</t>
+          <t>mymp.chartQuestions</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mymp.colExcused</t>
+          <t>mymp.colMP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Оправдано отсуство</t>
+          <t>Пратеник</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mungesë e arsyetuar</t>
+          <t>Deputeti</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Excused absence</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mymp.colUnexcused</t>
+          <t>mymp.colAttendance</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Неоправдано отсуство</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mungesa e pa arsyetuar</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Unexcused absence</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mymp.colDiscussions</t>
+          <t>mymp.colExcused</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Оправдано отсуство</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Mungesë e arsyetuar</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Excused absence</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mymp.colLaws</t>
+          <t>mymp.colUnexcused</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Неоправдано отсуство</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Mungesa e pa arsyetuar</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Unexcused absence</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mymp.colAmendments</t>
+          <t>mymp.colDiscussions</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mymp.colQuestions</t>
+          <t>mymp.colLaws</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Прашања</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pyetje</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mymp.colCommittees</t>
+          <t>mymp.colAmendments</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mymp.zeroQuestionsLabel</t>
+          <t>mymp.colQuestions</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Пратеници кои не поставиле ниту едно прашање</t>
+          <t>Прашања</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MPs who asked no questions at all</t>
+          <t>Questions</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mymp.top5Title</t>
+          <t>mymp.colCommittees</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Топ 5 најактивни пратеници</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Top 5 deputetët më aktivë</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Top 5 most active MPs</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mymp.top15Label</t>
+          <t>mymp.zeroQuestionsLabel</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Топ 15 —</t>
+          <t>Пратеници кои не поставиле ниту едно прашање</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>MPs who asked no questions at all</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mymp.compositeLabel</t>
+          <t>mymp.top5Title</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Вкупна активност</t>
+          <t>Топ 5 најактивни пратеници</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Top 5 deputetët më aktivë</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>Top 5 most active MPs</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mymp.onlyZero</t>
+          <t>mymp.top15Label</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Само без прашања</t>
+          <t>Топ 15 —</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vetëm pa pyetje</t>
+          <t>Top 15 —</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Only without questions</t>
+          <t>Top 15 —</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mymp.zeroSentence</t>
+          <t>mymp.compositeLabel</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
+          <t>Вкупна активност</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mymp.periodLabel</t>
+          <t>mymp.onlyZero</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Период</t>
+          <t>Само без прашања</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Periudha</t>
+          <t>Vetëm pa pyetje</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Only without questions</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>offices.title</t>
+          <t>mymp.zeroSentence</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>offices.subtitle</t>
+          <t>mymp.periodLabel</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
+          <t>Период</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
+          <t>Periudha</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
+          <t>Period</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>offices.kpiCases</t>
+          <t>offices.title</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Случаи</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Raste</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>offices.kpiMeetings</t>
+          <t>offices.subtitle</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Средби</t>
+          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Takime</t>
+          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>offices.kpiEvents</t>
+          <t>offices.kpiCases</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Настани</t>
+          <t>Случаи</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ngjarje</t>
+          <t>Raste</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Cases</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>offices.kpiInitiatives</t>
+          <t>offices.kpiMeetings</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Иницијативи</t>
+          <t>Средби</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Iniciativa</t>
+          <t>Takime</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>Meetings</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>offices.chartByMP</t>
+          <t>offices.kpiEvents</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Случаи по пратеник</t>
+          <t>Настани</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Raste sipas deputetit</t>
+          <t>Ngjarje</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cases by MP</t>
+          <t>Events</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>offices.chartByType</t>
+          <t>offices.kpiInitiatives</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Иницијативи</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Iniciativa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Initiatives</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>offices.chartByParty</t>
+          <t>offices.chartByMP</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Случаи по партија</t>
+          <t>Случаи по пратеник</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Raste sipas partisë</t>
+          <t>Raste sipas deputetit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cases by party</t>
+          <t>Cases by MP</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>offices.chartByGender</t>
+          <t>offices.chartByType</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Случаи по пол</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Raste sipas gjinisë</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cases by gender</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>offices.chartByAge</t>
+          <t>offices.chartByParty</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Случаи по возрасна група</t>
+          <t>Случаи по партија</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Raste sipas grupmoshës</t>
+          <t>Raste sipas partisë</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cases by age group</t>
+          <t>Cases by party</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>offices.chartByEthnicity</t>
+          <t>offices.chartByGender</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Случаи по етничка припадност</t>
+          <t>Случаи по пол</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raste sipas përkatësisë etnike</t>
+          <t>Raste sipas gjinisë</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cases by ethnicity</t>
+          <t>Cases by gender</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>offices.chartOverTime</t>
+          <t>offices.chartByAge</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Случаи по период</t>
+          <t>Случаи по возрасна група</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Raste sipas periudhës</t>
+          <t>Raste sipas grupmoshës</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cases over time</t>
+          <t>Cases by age group</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>offices.male</t>
+          <t>offices.chartByEthnicity</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Машки</t>
+          <t>Случаи по етничка припадност</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Meshkuj</t>
+          <t>Raste sipas përkatësisë etnike</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Cases by ethnicity</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>offices.female</t>
+          <t>offices.chartOverTime</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Женски</t>
+          <t>Случаи по период</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Femra</t>
+          <t>Raste sipas periudhës</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Cases over time</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>map.title</t>
+          <t>offices.chartByAgeNote</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Локации на канцеларии</t>
+          <t>Случаи по возрасна група на граѓаните</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Vendndodhjet e zyrave</t>
+          <t>Raste sipas grupmoshës së qytetarëve</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Office locations</t>
+          <t>Cases by age group of citizens</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>map.locatedSuffix</t>
+          <t>offices.chartByEthnicityNote</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>лоцирани канцеларии на мапата</t>
+          <t>Случаи по етничка припадност на граѓаните</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>zyra të lokalizuara në hartë</t>
+          <t>Raste sipas përkatësisë etnike të qytetarëve</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>offices located on the map</t>
+          <t>Cases by ethnicity of citizens</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>map.popupTitle</t>
+          <t>offices.male</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Канцеларија</t>
+          <t>Машки</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>Meshkuj</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>profile.title</t>
+          <t>offices.female</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Профил на пратеник</t>
+          <t>Женски</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Profili i deputetit</t>
+          <t>Femra</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>MP profile</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>profile.subtitle</t>
+          <t>offices.formerMP</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
+          <t>поранешен пратеник</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
+          <t>ish-deputet</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
+          <t>former MP</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>profile.sectionQuestions</t>
+          <t>map.title</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Парламентарни прашања</t>
+          <t>Локации на канцеларии</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pyetje parlamentare</t>
+          <t>Vendndodhjet e zyrave</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Office locations</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>profile.sectionActivity</t>
+          <t>map.locatedSuffix</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Активност во Собранието</t>
+          <t>лоцирани канцеларии на мапата</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Aktiviteti në Kuvend</t>
+          <t>zyra të lokalizuara në hartë</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Activity in the Assembly</t>
+          <t>offices located on the map</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>profile.sectionOffice</t>
+          <t>map.popupTitle</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Канцеларија за контакт</t>
+          <t>Канцеларија</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Zyra e kontaktit</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Contact office</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>profile.noOfficeData</t>
+          <t>profile.title</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
+          <t>Профил на пратеник</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
+          <t>Profili i deputetit</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>This MP has no recorded citizen cases.</t>
+          <t>MP profile</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>profile.noQuestionsData</t>
+          <t>profile.subtitle</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
+          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
+          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>This MP asked no questions in the current mandate.</t>
+          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>profile.questionsAsked</t>
+          <t>profile.sectionQuestions</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Парламентарни прашања</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Pyetje parlamentare</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>profile.plenaryAttendance</t>
+          <t>profile.sectionActivity</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Активност во Собранието</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Aktiviteti në Kuvend</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>Activity in the Assembly</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>profile.committees</t>
+          <t>profile.sectionOffice</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Канцеларија за контакт</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Zyra e kontaktit</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Contact office</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>profile.citizenCases</t>
+          <t>profile.noOfficeData</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Граѓански случаи</t>
+          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Raste qytetare</t>
+          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Citizen cases</t>
+          <t>This MP has no recorded citizen cases.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>profile.topInstitutions</t>
+          <t>profile.noQuestionsData</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Најчесто адресирани институции</t>
+          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Institucionet më të adresuara</t>
+          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Most frequently addressed institutions</t>
+          <t>This MP asked no questions in the current mandate.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>profile.recentQuestions</t>
+          <t>profile.questionsAsked</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Последни прашања</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pyetjet e fundit</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Recent questions</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>profile.casesByType</t>
+          <t>profile.plenaryAttendance</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>profile.independentBody</t>
+          <t>profile.committees</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Независно тело</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Organ i pavarur</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Independent body</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>profile.sort.name</t>
+          <t>profile.citizenCases</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Абецеден ред</t>
+          <t>Граѓански случаи</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rend alfabetik</t>
+          <t>Raste qytetare</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Alphabetical</t>
+          <t>Citizen cases</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>profile.sort.composite</t>
+          <t>profile.topInstitutions</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Општа активност</t>
+          <t>Најчесто адресирани институции</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Institucionet më të adresuara</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>Most frequently addressed institutions</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>profile.sort.questions</t>
+          <t>profile.recentQuestions</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Прашања (2024–28)</t>
+          <t>Последни прашања</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pyetje (2024–28)</t>
+          <t>Pyetjet e fundit</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Questions (2024–28)</t>
+          <t>Recent questions</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>profile.sort.attendance</t>
+          <t>profile.casesByType</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>profile.sort.discussions</t>
+          <t>profile.independentBody</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Независно тело</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Organ i pavarur</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Independent body</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>profile.sort.laws</t>
+          <t>profile.sort.name</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Абецеден ред</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Rend alfabetik</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Alphabetical</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>profile.sort.amendments</t>
+          <t>profile.sort.composite</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Општа активност</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>profile.sort.committees</t>
+          <t>profile.sort.questions</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Прашања (2024–28)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Pyetje (2024–28)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Questions (2024–28)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>home.pageTitle</t>
+          <t>profile.sort.attendance</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Парламентарни отворени податоци</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Të dhëna të hapura parlamentare</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Parliamentary open data</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>home.badge</t>
+          <t>profile.sort.discussions</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Собрание на Република Северна Македонија · 2024–2028</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>home.heroTitle</t>
+          <t>profile.sort.laws</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Интерактивен панел на отворени податоци</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Panel interaktiv i të dhënave të hapura</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Interactive open data dashboard</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>home.heroSubtitle</t>
+          <t>profile.sort.amendments</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>на Собранието на Република Северна Македонија</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>of the Assembly of the Republic of North Macedonia</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>home.kpiQuestions</t>
+          <t>profile.sort.committees</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pyetje deputetësh</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>home.kpiQuestionsNote</t>
+          <t>home.pageTitle</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>590 одговорени</t>
+          <t>Парламентарни отворени податоци</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>590 të përgjigjura</t>
+          <t>Të dhëna të hapura parlamentare</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>590 answered</t>
+          <t>Parliamentary open data</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>home.kpiMPs</t>
+          <t>home.badge</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>Собрание на Република Северна Македонија · 2024–2028</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>home.kpiMPsNote</t>
+          <t>home.heroTitle</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Активен состав 2024–2028</t>
+          <t>Интерактивен панел на отворени податоци</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Përbërja aktive 2024–2028</t>
+          <t>Panel interaktiv i të dhënave të hapura</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Active assembly 2024–2028</t>
+          <t>Interactive open data dashboard</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>home.kpiOffices</t>
+          <t>home.heroSubtitle</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Канцеларии</t>
+          <t>на Собранието на Република Северна Македонија</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Offices</t>
+          <t>of the Assembly of the Republic of North Macedonia</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>home.kpiOfficesNote</t>
+          <t>home.kpiQuestions</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>за контакт со граѓани</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>për kontakt me qytetarët</t>
+          <t>Pyetje deputetësh</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>for citizen contact</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>home.descQuestions</t>
+          <t>home.kpiQuestionsNote</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
+          <t>590 одговорени</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
+          <t>590 të përgjigjura</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
+          <t>590 answered</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>home.descMyMP</t>
+          <t>home.kpiMPs</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>home.descOffices</t>
+          <t>home.kpiMPsNote</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
+          <t>Активен состав 2024–2028</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
+          <t>Përbërja aktive 2024–2028</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
+          <t>Active assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>home.descProfile</t>
+          <t>home.kpiOffices</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
+          <t>Канцеларии</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Unified MP profile: parliamentary activity and citizen cases</t>
+          <t>Offices</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>home.open</t>
+          <t>home.kpiOfficesNote</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Отвори</t>
+          <t>за контакт со граѓани</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Hap</t>
+          <t>për kontakt me qytetarët</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>for citizen contact</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>home.disclaimerSupport</t>
+          <t>home.descQuestions</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
+          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
+          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
+          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPre</t>
+          <t>home.descMyMP</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Контролната табла користи податоци преземени од</t>
+          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paneli përdor të dhëna të marra nga</t>
+          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>The dashboard uses data sourced from</t>
+          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPost</t>
+          <t>home.descOffices</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
+          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
+          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
+          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>about.p1</t>
+          <t>home.descProfile</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
+          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
+          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
+          <t>Unified MP profile: parliamentary activity and citizen cases</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>about.p2</t>
+          <t>home.open</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
+          <t>Отвори</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
+          <t>Hap</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>about.p3</t>
+          <t>home.disclaimerSupport</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
+          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
+          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
+          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>about.goalsIntro</t>
+          <t>home.disclaimerDataPre</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
+          <t>Контролната табла користи податоци преземени од</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
+          <t>Paneli përdor të dhëna të marra nga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>In pursuing our vision and mission, our long-term goals are:</t>
+          <t>The dashboard uses data sourced from</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>about.goals.0</t>
+          <t>home.disclaimerDataPost</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Балансиран социо економски развој</t>
+          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Zhvillim i balancuar socio-ekonomik</t>
+          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Balanced socio-economic development</t>
+          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>about.goals.1</t>
+          <t>about.p1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Активна граѓанска вклученост</t>
+          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Përfshirje aktive qytetare</t>
+          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Active civic engagement</t>
+          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>about.goals.2</t>
+          <t>about.p2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Партиципативна политичка култура</t>
+          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Kulturë politike participative</t>
+          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Participative political culture</t>
+          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>about.goals.3</t>
+          <t>about.p3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Остварување на либерални вредности во општеството</t>
+          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Realizimi i vlerave liberale në shoqëri</t>
+          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Realising liberal values in society</t>
+          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>about.goals.4</t>
+          <t>about.goalsIntro</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Почит кон владеење на правото и доброто владеење</t>
+          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
+          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Respect for the rule of law and good governance</t>
+          <t>In pursuing our vision and mission, our long-term goals are:</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>about.goals.5</t>
+          <t>about.goals.0</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Промоција на одржливо образование</t>
+          <t>Балансиран социо економски развој</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Promovimi i arsimit të qëndrueshëm</t>
+          <t>Zhvillim i balancuar socio-ekonomik</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Promotion of sustainable education</t>
+          <t>Balanced socio-economic development</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>about.goals.6</t>
+          <t>about.goals.1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
+          <t>Активна граѓанска вклученост</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Realizimi i një procesi të vendimmarrjes së bazuar në dëshmi</t>
+          <t>Përfshirje aktive qytetare</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Achieving an evidence-based decision-making process</t>
+          <t>Active civic engagement</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>about.goals.7</t>
+          <t>about.goals.2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Мултиетничко и мултикултурно сопостоење</t>
+          <t>Партиципативна политичка култура</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bashkëjetesë multietnike dhe multikulturore</t>
+          <t>Kulturë politike participative</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Multi-ethnic and multicultural coexistence</t>
+          <t>Participative political culture</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>project.p1</t>
+          <t>about.goals.3</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
+          <t>Остварување на либерални вредности во општеството</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
+          <t>Realizimi i vlerave liberale në shoqëri</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
+          <t>Realising liberal values in society</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>project.p2</t>
+          <t>about.goals.4</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
+          <t>Почит кон владеење на правото и доброто владеење</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
+          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
+          <t>Respect for the rule of law and good governance</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>project.p3</t>
+          <t>about.goals.5</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
+          <t>Промоција на одржливо образование</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
+          <t>Promovimi i arsimit të qëndrueshëm</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
+          <t>Promotion of sustainable education</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>project.p4</t>
+          <t>about.goals.6</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество е поддржан преку грантовата шема Digital Spark, како дел од проектот Regional Support Mechanism EECA, спроведуван од Фондацијата Метаморфозис и TechSoup, во партнерство со CIVICUS и во рамки на Digital Democracy Initiative (DDI), која го опфаќа Глобалниот југ.</t>
+          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare mbështetet përmes skemës së granteve Digital Spark, si pjesë e projektit Regional Support Mechanism EECA, i zbatuar nga Fondacioni Metamorphosis dhe TechSoup, në partneritet me CIVICUS dhe në kuadër të Digital Democracy Initiative (DDI), e cila mbulon Jugun Global.</t>
+          <t>Realizimi i një procesi të vendimmarrjes së bazuar në dëshmi</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Assembly Open Data in Practice: Encouraging Citizen Participation, is supported through the Digital Spark granting scheme, as part of the Regional Support Mechanism EECA project, implemented by Metamorphosis Foundation and TechSoup, in partnership with CIVICUS and under the Digital Democracy Initiative (DDI) that covers the Global South.</t>
+          <t>Achieving an evidence-based decision-making process</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>methodology.title</t>
+          <t>about.goals.7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Методологија</t>
+          <t>Мултиетничко и мултикултурно сопостоење</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Metodologjia</t>
+          <t>Bashkëjetesë multietnike dhe multikulturore</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Multi-ethnic and multicultural coexistence</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>methodology.subtitle</t>
+          <t>project.p1</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Извори, ограничувања и процес на освежување</t>
+          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
+          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Sources, limitations and the update process</t>
+          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>methodology.formatLabel</t>
+          <t>project.p2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Формат</t>
+          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Formati</t>
+          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>methodology.recordsLabel</t>
+          <t>project.p3</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>записи</t>
+          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>regjistrime</t>
+          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>records</t>
+          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>methodology.lastPortalUpdate</t>
+          <t>project.p4</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Последно освежување на порталот</t>
+          <t>Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество е поддржан преку грантовата шема Digital Spark, како дел од проектот Regional Support Mechanism EECA, спроведуван од Фондацијата Метаморфозис и TechSoup, во партнерство со CIVICUS и во рамки на Digital Democracy Initiative (DDI), која го опфаќа Глобалниот југ.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Përditësimi i fundit i portalit</t>
+          <t>Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare mbështetet përmes skemës së granteve Digital Spark, si pjesë e projektit Regional Support Mechanism EECA, i zbatuar nga Fondacioni Metamorphosis dhe TechSoup, në partneritet me CIVICUS dhe në kuadër të Digital Democracy Initiative (DDI), e cila mbulon Jugun Global.</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Last portal update</t>
+          <t>Assembly Open Data in Practice: Encouraging Citizen Participation, is supported through the Digital Spark granting scheme, as part of the Regional Support Mechanism EECA project, implemented by Metamorphosis Foundation and TechSoup, in partnership with CIVICUS and under the Digital Democracy Initiative (DDI) that covers the Global South.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>methodology.sources.0.name</t>
+          <t>methodology.title</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Пратенички прашања 2024–2028</t>
+          <t>Методологија</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve 2024–2028</t>
+          <t>Metodologjia</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Parliamentary questions 2024–2028</t>
+          <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.0</t>
+          <t>methodology.subtitle</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
+          <t>Извори, ограничувања и процес на освежување</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
+          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
+          <t>Sources, limitations and the update process</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.1</t>
+          <t>methodology.formatLabel</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
+          <t>Формат</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
+          <t>Formati</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
+          <t>Format</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.2</t>
+          <t>methodology.recordsLabel</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
+          <t>записи</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
+          <t>regjistrime</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>91 records have no assigned institution — addressed to independent bodies.</t>
+          <t>records</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.3</t>
+          <t>methodology.lastPortalUpdate</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
+          <t>Последно освежување на порталот</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
+          <t>Përditësimi i fundit i portalit</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
+          <t>Last portal update</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>methodology.sources.1.name</t>
+          <t>methodology.sources.0.name</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
+          <t>Пратенички прашања 2024–2028</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
+          <t>Pyetjet e deputetëve 2024–2028</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
+          <t>Parliamentary questions 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.0</t>
+          <t>methodology.sources.0.notes.0</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
+          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
+          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Periodic report, not updated since November 2025.</t>
+          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.1</t>
+          <t>methodology.sources.0.notes.1</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
+          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
+          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>The XLSX file uses a three-row header structure with internal codes.</t>
+          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.2</t>
+          <t>methodology.sources.0.notes.2</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
+          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
+          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
+          <t>91 records have no assigned institution — addressed to independent bodies.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>methodology.sources.2.name</t>
+          <t>methodology.sources.0.notes.3</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.0</t>
+          <t>methodology.sources.1.name</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
+          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
+          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
+          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.1</t>
+          <t>methodology.sources.1.notes.0</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
+          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
+          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Format: tidy/long — each category is a separate row.</t>
+          <t>Periodic report, not updated since November 2025.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.2</t>
+          <t>methodology.sources.1.notes.1</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
+          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
+          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>The UUID identifier is used to join with the other datasets.</t>
+          <t>The XLSX file uses a three-row header structure with internal codes.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyTitle</t>
+          <t>methodology.sources.1.notes.2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Активен состав (120 пратеници)</t>
+          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Përbërja aktive (120 deputetë)</t>
+          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Active assembly (120 MPs)</t>
+          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP1</t>
+          <t>methodology.sources.2.name</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP2</t>
+          <t>methodology.sources.2.notes.0</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
+          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
+          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
+          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>methodology.joinTitle</t>
+          <t>methodology.sources.2.notes.1</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Поврзување на датасети</t>
+          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Lidhja e dataseteve</t>
+          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Joining the datasets</t>
+          <t>Format: tidy/long — each category is a separate row.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>methodology.joinP1</t>
+          <t>methodology.sources.2.notes.2</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
+          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
+          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
+          <t>The UUID identifier is used to join with the other datasets.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>methodology.joinP2</t>
+          <t>methodology.activeAssemblyTitle</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
+          <t>Активен состав (120 пратеници)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
+          <t>Përbërja aktive (120 deputetë)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
+          <t>Active assembly (120 MPs)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>methodology.refreshTitle</t>
+          <t>methodology.activeAssemblyP1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Процес на освежување</t>
+          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Procesi i përditësimit</t>
+          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Update process</t>
+          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>methodology.refreshIntro</t>
+          <t>methodology.activeAssemblyP2</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
+          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
+          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
+          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1pre</t>
+          <t>methodology.joinTitle</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>Поврзување на датасети</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>Lidhja e dataseteve</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>Joining the datasets</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1post</t>
+          <t>methodology.joinP1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ги презема новите датотеки од CKAN API.</t>
+          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>i merr skedarët e rinj nga CKAN API.</t>
+          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>fetches the new files from the CKAN API.</t>
+          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2pre</t>
+          <t>methodology.joinP2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2post</t>
+          <t>methodology.refreshTitle</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ги обработува и генерира чисти JSON датотеки.</t>
+          <t>Процес на освежување</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
+          <t>Procesi i përditësimit</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>processes them and generates clean JSON files.</t>
+          <t>Update process</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>methodology.refreshStep3</t>
+          <t>methodology.refreshIntro</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>The system automatically rebuilds and deploys the dashboard.</t>
+          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
+          <t>methodology.refreshStep1pre</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Скриптата</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Skripta</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>The script</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>methodology.refreshStep1post</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ги презема новите датотеки од CKAN API.</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>i merr skedarët e rinj nga CKAN API.</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>fetches the new files from the CKAN API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>methodology.refreshStep2pre</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Скриптата</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Skripta</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>The script</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>methodology.refreshStep2post</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ги обработува и генерира чисти JSON датотеки.</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>processes them and generates clean JSON files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>methodology.refreshStep3</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>The system automatically rebuilds and deploys the dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
           <t>methodology.lastProcessedLabel</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Dashboard последно обработен:</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>Paneli i përpunuar së fundi:</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>Dashboard last processed:</t>
         </is>
@@ -8588,6 +8699,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Македонец</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Maqedonas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Macedonian</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Албанец</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Shqiptar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Albanian</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Турчин</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Turk</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ром</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rom</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Србин</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Serb</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Serbian</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Бошњак</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Boshnjak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bosniak</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Влав</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Vllah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vlach</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/translations.xlsx
+++ b/translations.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -507,4746 +507,4812 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nav.questions</t>
+          <t>consent.text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>Користиме колачиња за анонимна статистика на посетеноста (Google Analytics).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve</t>
+          <t>Përdorim cookie për statistika anonime të vizitave (Google Analytics).</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>We use cookies for anonymous visitor analytics (Google Analytics).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nav.mymp</t>
+          <t>consent.accept</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Активност на пратеник</t>
+          <t>Прифаќам</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetit</t>
+          <t>Pranoj</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MP activity</t>
+          <t>Accept</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nav.offices</t>
+          <t>consent.decline</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт</t>
+          <t>Одбивам</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit</t>
+          <t>Refuzoj</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Contact offices</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nav.profile</t>
+          <t>nav.questions</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Профил на пратеник</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Profili i deputetit</t>
+          <t>Pyetjet e deputetëve</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MP profile</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nav.methodology</t>
+          <t>nav.mymp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Методологија</t>
+          <t>Активност на пратеник</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Metodologjia</t>
+          <t>Aktiviteti i deputetit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>MP activity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nav.project</t>
+          <t>nav.offices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>За проектот</t>
+          <t>Канцеларии за контакт</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rreth projektit</t>
+          <t>Zyrat e kontaktit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>About the project</t>
+          <t>Contact offices</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nav.about</t>
+          <t>nav.profile</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>За ИДСЦС</t>
+          <t>Профил на пратеник</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rreth IDSCS</t>
+          <t>Profili i deputetit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>About IDSCS</t>
+          <t>MP profile</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nav.home</t>
+          <t>nav.methodology</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Почетна</t>
+          <t>Методологија</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ballina</t>
+          <t>Metodologjia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nav.language</t>
+          <t>nav.project</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Јазик</t>
+          <t>За проектот</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gjuha</t>
+          <t>Rreth projektit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>About the project</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>common.filterByMP</t>
+          <t>nav.about</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Избери пратеник</t>
+          <t>За ИДСЦС</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zgjidhni deputetin</t>
+          <t>Rreth IDSCS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Select MP</t>
+          <t>About IDSCS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>common.filterByParty</t>
+          <t>nav.home</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Избери партија</t>
+          <t>Почетна</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zgjidhni partinë</t>
+          <t>Ballina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Select party</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>common.filterByInstitution</t>
+          <t>nav.language</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Избери институција</t>
+          <t>Јазик</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zgjidhni institucionin</t>
+          <t>Gjuha</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Select institution</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>common.filterByStatus</t>
+          <t>common.filterByMP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Избери статус</t>
+          <t>Избери пратеник</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zgjidhni statusin</t>
+          <t>Zgjidhni deputetin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Select status</t>
+          <t>Select MP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>common.filterByPeriod</t>
+          <t>common.filterByParty</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Избери период</t>
+          <t>Избери партија</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zgjidhni periudhën</t>
+          <t>Zgjidhni partinë</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Select period</t>
+          <t>Select party</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>common.search</t>
+          <t>common.filterByInstitution</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Пребарај</t>
+          <t>Избери институција</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kërko</t>
+          <t>Zgjidhni institucionin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Select institution</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>common.download</t>
+          <t>common.filterByStatus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Преземи</t>
+          <t>Избери статус</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shkarko</t>
+          <t>Zgjidhni statusin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Select status</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>common.downloadCSV</t>
+          <t>common.filterByPeriod</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Преземи податоци (CSV)</t>
+          <t>Избери период</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shkarko të dhënat (CSV)</t>
+          <t>Zgjidhni periudhën</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Download data (CSV)</t>
+          <t>Select period</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>common.downloadPNG</t>
+          <t>common.search</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Преземи слика (PNG)</t>
+          <t>Пребарај</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shkarko imazhin (PNG)</t>
+          <t>Kërko</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Download image (PNG)</t>
+          <t>Search</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>common.downloadJSON</t>
+          <t>common.download</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Преземи JSON</t>
+          <t>Преземи</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shkarko JSON</t>
+          <t>Shkarko</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Download JSON</t>
+          <t>Download</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>common.lastUpdated</t>
+          <t>common.downloadCSV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Последно освежување</t>
+          <t>Преземи податоци (CSV)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Përditësimi i fundit</t>
+          <t>Shkarko të dhënat (CSV)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Last updated</t>
+          <t>Download data (CSV)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>common.noData</t>
+          <t>common.downloadPNG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Нема податоци</t>
+          <t>Преземи слика (PNG)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nuk ka të dhëna</t>
+          <t>Shkarko imazhin (PNG)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>Download image (PNG)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>common.allMPs</t>
+          <t>common.downloadJSON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Сите пратеници</t>
+          <t>Преземи JSON</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Të gjithë deputetët</t>
+          <t>Shkarko JSON</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>All MPs</t>
+          <t>Download JSON</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>common.allParties</t>
+          <t>common.lastUpdated</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Сите партии</t>
+          <t>Последно освежување</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Të gjitha partitë</t>
+          <t>Përditësimi i fundit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>All parties</t>
+          <t>Last updated</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>common.total</t>
+          <t>common.noData</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Вкупно</t>
+          <t>Нема податоци</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gjithsej</t>
+          <t>Nuk ka të dhëna</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>No data</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>common.showAll</t>
+          <t>common.allMPs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Прикажи ги сите</t>
+          <t>Сите пратеници</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shfaq të gjithë</t>
+          <t>Të gjithë deputetët</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Show all</t>
+          <t>All MPs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>common.showLess</t>
+          <t>common.allParties</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Прикажи помалку</t>
+          <t>Сите партии</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shfaq më pak</t>
+          <t>Të gjitha partitë</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Show less</t>
+          <t>All parties</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>common.of</t>
+          <t>common.total</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>од</t>
+          <t>Вкупно</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nga</t>
+          <t>Gjithsej</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>common.answered</t>
+          <t>common.showAll</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Одговорено</t>
+          <t>Прикажи ги сите</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Përgjigjur</t>
+          <t>Shfaq të gjithë</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Answered</t>
+          <t>Show all</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>common.pending</t>
+          <t>common.showLess</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Доставено</t>
+          <t>Прикажи помалку</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dërguar</t>
+          <t>Shfaq më pak</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Show less</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>common.sessions</t>
+          <t>common.of</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Седници</t>
+          <t>од</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seanca</t>
+          <t>nga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>of</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>common.source</t>
+          <t>common.answered</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Извор</t>
+          <t>Одговорено</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Burimi</t>
+          <t>Përgjigjur</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Answered</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>common.party</t>
+          <t>common.pending</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Партија</t>
+          <t>Доставено</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Partia</t>
+          <t>Dërguar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Party</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>common.category</t>
+          <t>common.sessions</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Категорија</t>
+          <t>Седници</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kategoria</t>
+          <t>Seanca</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>common.subcategory</t>
+          <t>common.source</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Подкатегорија</t>
+          <t>Извор</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nënkategoria</t>
+          <t>Burimi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>common.filter</t>
+          <t>common.party</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Филтер</t>
+          <t>Партија</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Filtër</t>
+          <t>Partia</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Party</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>common.sortBy</t>
+          <t>common.category</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Сортирај по</t>
+          <t>Категорија</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rendit sipas</t>
+          <t>Kategoria</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sort by</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>common.results</t>
+          <t>common.subcategory</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>резултати</t>
+          <t>Подкатегорија</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rezultate</t>
+          <t>Nënkategoria</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>Subcategory</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>common.close</t>
+          <t>common.filter</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Затвори</t>
+          <t>Филтер</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mbyll</t>
+          <t>Filtër</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Filter</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>common.prev</t>
+          <t>common.sortBy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Претходни</t>
+          <t>Сортирај по</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Të mëparshme</t>
+          <t>Rendit sipas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Previous</t>
+          <t>Sort by</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>common.next</t>
+          <t>common.results</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Следни</t>
+          <t>резултати</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Të mëtejshme</t>
+          <t>rezultate</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>results</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>common.mpsLower</t>
+          <t>common.close</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>пратеници</t>
+          <t>Затвори</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>deputetë</t>
+          <t>Mbyll</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>common.skipToContent</t>
+          <t>common.prev</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Прескокни на содржината</t>
+          <t>Претходни</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kalo te përmbajtja</t>
+          <t>Të mëparshme</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Skip to content</t>
+          <t>Previous</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>footer.dataNotePre</t>
+          <t>common.next</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Податоците се преземени од</t>
+          <t>Следни</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Të dhënat janë marrë nga</t>
+          <t>Të mëtejshme</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Data is sourced from</t>
+          <t>Next</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>footer.portalName</t>
+          <t>common.mpsLower</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Порталот за отворени податоци на Собранието на Република Северна Македонија</t>
+          <t>пратеници</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut</t>
+          <t>deputetë</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>the Open Data Portal of the Assembly of the Republic of North Macedonia</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>footer.dataNotePost</t>
+          <t>common.skipToContent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>, во формата и содржината во која тие се објавени од Собранието.</t>
+          <t>Прескокни на содржината</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
+          <t>Kalo te përmbajtja</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>, in the form and content in which it is published by the Assembly.</t>
+          <t>Skip to content</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>questions.title</t>
+          <t>footer.dataNotePre</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>Податоците се преземени од</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve</t>
+          <t>Të dhënat janë marrë nga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Data is sourced from</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>questions.subtitle</t>
+          <t>footer.portalName</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Прашања поставени во Собранието 2024–2028</t>
+          <t>Порталот за отворени податоци на Собранието на Република Северна Македонија</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara në Kuvend 2024–2028</t>
+          <t>Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Questions raised in the Assembly 2024–2028</t>
+          <t>the Open Data Portal of the Assembly of the Republic of North Macedonia</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>questions.kpiTotal</t>
+          <t>footer.dataNotePost</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Вкупно прашања</t>
+          <t>, во формата и содржината во која тие се објавени од Собранието.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gjithsej pyetje</t>
+          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Total questions</t>
+          <t>, in the form and content in which it is published by the Assembly.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>questions.kpiAnswered</t>
+          <t>questions.title</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Одговорени</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Të përgjigjura</t>
+          <t>Pyetjet e deputetëve</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Answered</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>questions.kpiPending</t>
+          <t>questions.subtitle</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Во тек</t>
+          <t>Прашања поставени во Собранието 2024–2028</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Në pritje</t>
+          <t>Pyetje të parashtruara në Kuvend 2024–2028</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Questions raised in the Assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>questions.kpiSessions</t>
+          <t>questions.kpiTotal</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Опфатени седници</t>
+          <t>Вкупно прашања</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seanca të përfshira</t>
+          <t>Gjithsej pyetje</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sessions covered</t>
+          <t>Total questions</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>questions.chartByMP</t>
+          <t>questions.kpiAnswered</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Прашања по пратеник</t>
+          <t>Одговорени</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pyetje sipas deputetit</t>
+          <t>Të përgjigjura</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Questions by MP</t>
+          <t>Answered</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>questions.chartByInstitution</t>
+          <t>questions.kpiPending</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Прашања по институција</t>
+          <t>Во тек</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pyetje sipas institucionit</t>
+          <t>Në pritje</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Questions by institution</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>questions.chartAnsweredVsPending</t>
+          <t>questions.kpiSessions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Одговорени наспроти во тек — по институција</t>
+          <t>Опфатени седници</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Të përgjigjura kundrejt në pritje — sipas institucionit</t>
+          <t>Seanca të përfshira</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Answered vs. pending — by institution</t>
+          <t>Sessions covered</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>questions.chartAnswerRate</t>
+          <t>questions.chartByMP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Стапка на одговарање по институција</t>
+          <t>Прашања по пратеник</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Shkalla e përgjigjes sipas institucionit</t>
+          <t>Pyetje sipas deputetit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Answer rate by institution</t>
+          <t>Questions by MP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>questions.chartAnswerRateNote</t>
+          <t>questions.chartByInstitution</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Сортирани по најмала стапка — кои институции ги одложуваат одговорите</t>
+          <t>Прашања по институција</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Të renditura sipas shkallës më të ulët — cilat institucione vonojnë përgjigjet</t>
+          <t>Pyetje sipas institucionit</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sorted by lowest rate — which institutions delay their answers</t>
+          <t>Questions by institution</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>questions.chartByParty</t>
+          <t>questions.chartAnsweredVsPending</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Прашања по партија</t>
+          <t>Одговорени наспроти во тек — по институција</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pyetje sipas grupit parlamentar</t>
+          <t>Të përgjigjura kundrejt në pritje — sipas institucionit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Questions by party</t>
+          <t>Answered vs. pending — by institution</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>questions.chartByPartyNote</t>
+          <t>questions.chartAnswerRate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Вкупно прашања по партија, со стапка на одговарање</t>
+          <t>Стапка на одговарање по институција</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gjithsej pyetje sipas partisë, me shkallën e përgjigjes</t>
+          <t>Shkalla e përgjigjes sipas institucionit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Total questions by party, with answer rate</t>
+          <t>Answer rate by institution</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>questions.chartTimeline</t>
+          <t>questions.chartAnswerRateNote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Прашања по седница</t>
+          <t>Сортирани по најмала стапка — кои институции ги одложуваат одговорите</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pyetje sipas seancës</t>
+          <t>Të renditura sipas shkallës më të ulët — cilat institucione vonojnë përgjigjet</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Questions by session</t>
+          <t>Sorted by lowest rate — which institutions delay their answers</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>questions.sessionFull</t>
+          <t>questions.chartByParty</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Седница бр.</t>
+          <t>Прашања по партија</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seanca nr.</t>
+          <t>Pyetje sipas grupit parlamentar</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Session no.</t>
+          <t>Questions by party</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>questions.questionsShort</t>
+          <t>questions.chartByPartyNote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>прашања</t>
+          <t>Вкупно прашања по партија, со стапка на одговарање</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>pyetje</t>
+          <t>Gjithsej pyetje sipas partisë, me shkallën e përgjigjes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Total questions by party, with answer rate</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>questions.tableQuestion</t>
+          <t>questions.chartTimeline</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Прашање</t>
+          <t>Прашања по седница</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pyetje</t>
+          <t>Pyetje sipas seancës</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Questions by session</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>questions.tableFrom</t>
+          <t>questions.sessionFull</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Пратеник</t>
+          <t>Седница бр.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Deputeti</t>
+          <t>Seanca nr.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Session no.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>questions.tableTo</t>
+          <t>questions.questionsShort</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Институција</t>
+          <t>прашања</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Institucioni</t>
+          <t>pyetje</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Institution</t>
+          <t>questions</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>questions.tableDate</t>
+          <t>questions.tableQuestion</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Датум</t>
+          <t>Прашање</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Question</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>questions.tableStatus</t>
+          <t>questions.tableFrom</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Пратеник</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Statusi</t>
+          <t>Deputeti</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>questions.detailTitle</t>
+          <t>questions.tableTo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Детали за прашањето</t>
+          <t>Институција</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Detajet e pyetjes</t>
+          <t>Institucioni</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Question details</t>
+          <t>Institution</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>questions.detailQuestion</t>
+          <t>questions.tableDate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Прашање</t>
+          <t>Датум</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pyetja</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>questions.detailAnswer</t>
+          <t>questions.tableStatus</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Одговор</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Përgjigja</t>
+          <t>Statusi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>questions.detailNoAnswer</t>
+          <t>questions.detailTitle</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Одговорот сè уште не е доставен.</t>
+          <t>Детали за прашањето</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Përgjigja ende nuk është dorëzuar.</t>
+          <t>Detajet e pyetjes</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>The answer has not been submitted yet.</t>
+          <t>Question details</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>questions.detailNoAnswerSource</t>
+          <t>questions.detailQuestion</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Забелешка: Во изворните податоци објавени од Собранието, ова пратеничко прашање е означено како одговорено, но во полето предвидено за одговор повторно е ставен текстот на самото прашање.</t>
+          <t>Прашање</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Shënim: Në të dhënat burimore të publikuara nga Kuvendi, kjo pyetje parlamentare është shënuar si e përgjigjur, por në fushën e parashikuar për përgjigje është vendosur përsëri teksti i vetë pyetjes.</t>
+          <t>Pyetja</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Note: In the source data published by the Assembly, this parliamentary question is marked as answered, but the field intended for the answer again contains the text of the question itself.</t>
+          <t>Question</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>questions.nullInstitution</t>
+          <t>questions.detailAnswer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Независно тело</t>
+          <t>Одговор</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Organ i pavarur</t>
+          <t>Përgjigja</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Independent body</t>
+          <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>questions.nullDate</t>
+          <t>questions.detailNoAnswer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Датумот не е назначен</t>
+          <t>Одговорот сè уште не е доставен.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Data nuk është caktuar</t>
+          <t>Përgjigja ende nuk është dorëzuar.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Date not assigned</t>
+          <t>The answer has not been submitted yet.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>questions.openDetailAria</t>
+          <t>questions.detailNoAnswerSource</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Отвори детали за прашање од</t>
+          <t>Забелешка: Во изворните податоци објавени од Собранието, ова пратеничко прашање е означено како одговорено, но во полето предвидено за одговор повторно е ставен текстот на самото прашање.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hap detajet e pyetjes nga</t>
+          <t>Shënim: Në të dhënat burimore të publikuara nga Kuvendi, kjo pyetje parlamentare është shënuar si e përgjigjur, por në fushën e parashikuar për përgjigje është vendosur përsëri teksti i vetë pyetjes.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Open question details from</t>
+          <t>Note: In the source data published by the Assembly, this parliamentary question is marked as answered, but the field intended for the answer again contains the text of the question itself.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>questions.session</t>
+          <t>questions.nullInstitution</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Седница</t>
+          <t>Независно тело</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seanca</t>
+          <t>Organ i pavarur</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Independent body</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>questions.autoTranslated</t>
+          <t>questions.nullDate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Автоматски превод</t>
+          <t>Датумот не е назначен</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Përkthim automatik</t>
+          <t>Data nuk është caktuar</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Machine-translated</t>
+          <t>Date not assigned</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>questions.aiTranslationNotice</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>questions.openDetailAria</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Отвори детали за прашање од</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Përkthimi në gjuhën shqipe i pyetjeve parlamentare është përgatitur me ndihmën e mjeteve të inteligjencës artificiale (AI), duke u bazuar në materialet e disponueshme në gjuhën maqedonase në Portalin e të Dhënave të Hapura të Kuvendit. Deri në ditën e publikimit, materialet në portal ishin të disponueshme vetëm në gjuhën maqedonase.</t>
+          <t>Hap detajet e pyetjes nga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>The English translation of the parliamentary questions was prepared using artificial intelligence (AI) tools, based on the materials available in Macedonian on the Assembly Open Data Portal. As of the date of publication, the materials on the portal were available only in Macedonian.</t>
+          <t>Open question details from</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mymp.title</t>
+          <t>questions.session</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Активност на пратеник</t>
+          <t>Седница</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetit</t>
+          <t>Seanca</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MP activity</t>
+          <t>Session</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mymp.subtitle</t>
+          <t>questions.autoTranslated</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
+          <t>Автоматски превод</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
+          <t>Përkthim automatik</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MP activity for the period January–June 2025</t>
+          <t>Machine-translated</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mymp.stalenessNote</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
-        </is>
-      </c>
+          <t>questions.aiTranslationNotice</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
+          <t>Përkthimi në gjuhën shqipe i pyetjeve parlamentare është përgatitur me ndihmën e mjeteve të inteligjencës artificiale (AI), duke u bazuar në materialet e disponueshme në gjuhën maqedonase në Portalin e të Dhënave të Hapura të Kuvendit. Deri në ditën e publikimit, materialet në portal ishin të disponueshme vetëm në gjuhën maqedonase.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
+          <t>The English translation of the parliamentary questions was prepared using artificial intelligence (AI) tools, based on the materials available in Macedonian on the Assembly Open Data Portal. As of the date of publication, the materials on the portal were available only in Macedonian.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mymp.mostActiveTitle</t>
+          <t>mymp.title</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Најактивен пратеник</t>
+          <t>Активност на пратеник</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Deputeti më aktiv</t>
+          <t>Aktiviteti i deputetit</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Most active MP</t>
+          <t>MP activity</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mymp.mostActiveNote</t>
+          <t>mymp.subtitle</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
+          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
+          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
+          <t>MP activity for the period January–June 2025</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mymp.kpiMPs</t>
+          <t>mymp.stalenessNote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mymp.newlySeatedNote</t>
+          <t>mymp.mostActiveTitle</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>стапиле на должност по периодот на извештајот</t>
+          <t>Најактивен пратеник</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>kanë marrë mandatin pas periudhës së raportit</t>
+          <t>Deputeti më aktiv</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>took office after the reporting period</t>
+          <t>Most active MP</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mymp.noPeriodData</t>
+          <t>mymp.mostActiveNote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Стапил на должност по последниот извештај за активност</t>
+          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
+          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Took office after the latest activity report</t>
+          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mymp.kpiAvgAttendance</t>
+          <t>mymp.kpiMPs</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Просечно присуство</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prezenca mesatare</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Average attendance</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mymp.kpiZeroQuestions</t>
+          <t>mymp.newlySeatedNote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Пратеници без прашања</t>
+          <t>стапиле на должност по периодот на извештајот</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Deputetë pa pyetje</t>
+          <t>kanë marrë mandatin pas periudhës së raportit</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MPs with no questions</t>
+          <t>took office after the reporting period</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mymp.chartAttendance</t>
+          <t>mymp.noPeriodData</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Стапил на должност по последниот извештај за активност</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>Took office after the latest activity report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mymp.chartDiscussions</t>
+          <t>mymp.kpiAvgAttendance</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Просечно присуство</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Prezenca mesatare</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Average attendance</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mymp.chartQuestions</t>
+          <t>mymp.kpiZeroQuestions</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Пратеници без прашања</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Deputetë pa pyetje</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>MPs with no questions</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mymp.colMP</t>
+          <t>mymp.chartAttendance</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Пратеник</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Deputeti</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mymp.colAttendance</t>
+          <t>mymp.chartDiscussions</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mymp.colExcused</t>
+          <t>mymp.chartQuestions</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Оправдано отсуство</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mungesë e arsyetuar</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Excused absence</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mymp.colUnexcused</t>
+          <t>mymp.colMP</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Неоправдано отсуство</t>
+          <t>Пратеник</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mungesa e pa arsyetuar</t>
+          <t>Deputeti</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Unexcused absence</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mymp.colDiscussions</t>
+          <t>mymp.colAttendance</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mymp.colLaws</t>
+          <t>mymp.colExcused</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Оправдано отсуство</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Mungesë e arsyetuar</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Excused absence</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mymp.colAmendments</t>
+          <t>mymp.colUnexcused</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Неоправдано отсуство</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Mungesa e pa arsyetuar</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Unexcused absence</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mymp.colQuestions</t>
+          <t>mymp.colDiscussions</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Прашања</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pyetje</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mymp.colCommittees</t>
+          <t>mymp.colLaws</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mymp.zeroQuestionsLabel</t>
+          <t>mymp.colAmendments</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Пратеници кои не поставиле ниту едно прашање</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MPs who asked no questions at all</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mymp.top5Title</t>
+          <t>mymp.colQuestions</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Топ 5 најактивни пратеници</t>
+          <t>Прашања</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Top 5 deputetët më aktivë</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Top 5 most active MPs</t>
+          <t>Questions</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mymp.top15Label</t>
+          <t>mymp.colCommittees</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Топ 15 —</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mymp.compositeLabel</t>
+          <t>mymp.zeroQuestionsLabel</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Вкупна активност</t>
+          <t>Пратеници кои не поставиле ниту едно прашање</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>MPs who asked no questions at all</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mymp.onlyZero</t>
+          <t>mymp.top5Title</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Само без прашања</t>
+          <t>Топ 5 најактивни пратеници</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Vetëm pa pyetje</t>
+          <t>Top 5 deputetët më aktivë</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Only without questions</t>
+          <t>Top 5 most active MPs</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mymp.zeroSentence</t>
+          <t>mymp.top15Label</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
+          <t>Топ 15 —</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
+          <t>Top 15 —</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
+          <t>Top 15 —</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mymp.periodLabel</t>
+          <t>mymp.compositeLabel</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Период</t>
+          <t>Вкупна активност</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Periudha</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>offices.title</t>
+          <t>mymp.onlyZero</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>Само без прашања</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>Vetëm pa pyetje</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>Only without questions</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>offices.subtitle</t>
+          <t>mymp.zeroSentence</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
+          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
+          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
+          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>offices.kpiCases</t>
+          <t>mymp.periodLabel</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Случаи</t>
+          <t>Период</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Raste</t>
+          <t>Periudha</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Period</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>offices.kpiMeetings</t>
+          <t>offices.title</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Средби</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Takime</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>offices.kpiEvents</t>
+          <t>offices.subtitle</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Настани</t>
+          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ngjarje</t>
+          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>offices.kpiInitiatives</t>
+          <t>offices.kpiCases</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Иницијативи</t>
+          <t>Случаи</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Iniciativa</t>
+          <t>Raste</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>Cases</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>offices.chartByMP</t>
+          <t>offices.kpiMeetings</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Случаи по пратеник</t>
+          <t>Средби</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Raste sipas deputetit</t>
+          <t>Takime</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cases by MP</t>
+          <t>Meetings</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>offices.chartByType</t>
+          <t>offices.kpiEvents</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Настани</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Ngjarje</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Events</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>offices.chartByParty</t>
+          <t>offices.kpiInitiatives</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Случаи по партија</t>
+          <t>Иницијативи</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Raste sipas partisë</t>
+          <t>Iniciativa</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cases by party</t>
+          <t>Initiatives</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>offices.chartByGender</t>
+          <t>offices.chartByMP</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Случаи по пол</t>
+          <t>Случаи по пратеник</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raste sipas gjinisë</t>
+          <t>Raste sipas deputetit</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cases by gender</t>
+          <t>Cases by MP</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>offices.chartByAge</t>
+          <t>offices.chartByType</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Случаи по возрасна група</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Raste sipas grupmoshës</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cases by age group</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>offices.chartByEthnicity</t>
+          <t>offices.chartByParty</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Случаи по етничка припадност</t>
+          <t>Случаи по партија</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raste sipas përkatësisë etnike</t>
+          <t>Raste sipas partisë</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cases by ethnicity</t>
+          <t>Cases by party</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>offices.chartOverTime</t>
+          <t>offices.chartByGender</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Случаи по период</t>
+          <t>Случаи по пол</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Raste sipas periudhës</t>
+          <t>Raste sipas gjinisë</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cases over time</t>
+          <t>Cases by gender</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>offices.chartByAgeNote</t>
+          <t>offices.chartByAge</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Случаи по возрасна група на граѓаните</t>
+          <t>Случаи по возрасна група</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Raste sipas grupmoshës së qytetarëve</t>
+          <t>Raste sipas grupmoshës</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cases by age group of citizens</t>
+          <t>Cases by age group</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>offices.chartByEthnicityNote</t>
+          <t>offices.chartByEthnicity</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Случаи по етничка припадност на граѓаните</t>
+          <t>Случаи по етничка припадност</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raste sipas përkatësisë etnike të qytetarëve</t>
+          <t>Raste sipas përkatësisë etnike</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cases by ethnicity of citizens</t>
+          <t>Cases by ethnicity</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>offices.male</t>
+          <t>offices.chartOverTime</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Машки</t>
+          <t>Случаи по период</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Meshkuj</t>
+          <t>Raste sipas periudhës</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Cases over time</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>offices.female</t>
+          <t>offices.chartByAgeNote</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Женски</t>
+          <t>Случаи по возрасна група на граѓаните</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Femra</t>
+          <t>Raste sipas grupmoshës së qytetarëve</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Cases by age group of citizens</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>offices.formerMP</t>
+          <t>offices.chartByEthnicityNote</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>поранешен пратеник</t>
+          <t>Случаи по етничка припадност на граѓаните</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ish-deputet</t>
+          <t>Raste sipas përkatësisë etnike të qytetarëve</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>former MP</t>
+          <t>Cases by ethnicity of citizens</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>map.title</t>
+          <t>offices.male</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Локации на канцеларии</t>
+          <t>Машки</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Vendndodhjet e zyrave</t>
+          <t>Meshkuj</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Office locations</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>map.locatedSuffix</t>
+          <t>offices.female</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>лоцирани канцеларии на мапата</t>
+          <t>Женски</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>zyra të lokalizuara në hartë</t>
+          <t>Femra</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>offices located on the map</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>map.popupTitle</t>
+          <t>offices.formerMP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Канцеларија</t>
+          <t>поранешен пратеник</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>ish-deputet</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>former MP</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>profile.title</t>
+          <t>map.title</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Профил на пратеник</t>
+          <t>Локации на канцеларии</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Profili i deputetit</t>
+          <t>Vendndodhjet e zyrave</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MP profile</t>
+          <t>Office locations</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>profile.subtitle</t>
+          <t>map.locatedSuffix</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
+          <t>лоцирани канцеларии на мапата</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
+          <t>zyra të lokalizuara në hartë</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
+          <t>offices located on the map</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>profile.sectionQuestions</t>
+          <t>map.popupTitle</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Парламентарни прашања</t>
+          <t>Канцеларија</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pyetje parlamentare</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>profile.sectionActivity</t>
+          <t>profile.title</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Активност во Собранието</t>
+          <t>Профил на пратеник</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Aktiviteti në Kuvend</t>
+          <t>Profili i deputetit</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Activity in the Assembly</t>
+          <t>MP profile</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>profile.sectionOffice</t>
+          <t>profile.subtitle</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Канцеларија за контакт</t>
+          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Zyra e kontaktit</t>
+          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Contact office</t>
+          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>profile.noOfficeData</t>
+          <t>profile.sectionQuestions</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
+          <t>Парламентарни прашања</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
+          <t>Pyetje parlamentare</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>This MP has no recorded citizen cases.</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>profile.noQuestionsData</t>
+          <t>profile.sectionActivity</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
+          <t>Активност во Собранието</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
+          <t>Aktiviteti në Kuvend</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>This MP asked no questions in the current mandate.</t>
+          <t>Activity in the Assembly</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>profile.questionsAsked</t>
+          <t>profile.sectionOffice</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Канцеларија за контакт</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Zyra e kontaktit</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>Contact office</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>profile.plenaryAttendance</t>
+          <t>profile.noOfficeData</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>This MP has no recorded citizen cases.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>profile.committees</t>
+          <t>profile.noQuestionsData</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>This MP asked no questions in the current mandate.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>profile.citizenCases</t>
+          <t>profile.questionsAsked</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Граѓански случаи</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Raste qytetare</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Citizen cases</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>profile.topInstitutions</t>
+          <t>profile.plenaryAttendance</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Најчесто адресирани институции</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Institucionet më të adresuara</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Most frequently addressed institutions</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>profile.recentQuestions</t>
+          <t>profile.committees</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Последни прашања</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pyetjet e fundit</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Recent questions</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>profile.casesByType</t>
+          <t>profile.citizenCases</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Граѓански случаи</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Raste qytetare</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Citizen cases</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>profile.independentBody</t>
+          <t>profile.topInstitutions</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Независно тело</t>
+          <t>Најчесто адресирани институции</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Organ i pavarur</t>
+          <t>Institucionet më të adresuara</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Independent body</t>
+          <t>Most frequently addressed institutions</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>profile.sort.name</t>
+          <t>profile.recentQuestions</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Абецеден ред</t>
+          <t>Последни прашања</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Rend alfabetik</t>
+          <t>Pyetjet e fundit</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Alphabetical</t>
+          <t>Recent questions</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>profile.sort.composite</t>
+          <t>profile.casesByType</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Општа активност</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>profile.sort.questions</t>
+          <t>profile.independentBody</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Прашања (2024–28)</t>
+          <t>Независно тело</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pyetje (2024–28)</t>
+          <t>Organ i pavarur</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Questions (2024–28)</t>
+          <t>Independent body</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>profile.sort.attendance</t>
+          <t>profile.sort.name</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Абецеден ред</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Rend alfabetik</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Alphabetical</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>profile.sort.discussions</t>
+          <t>profile.sort.composite</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Општа активност</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>profile.sort.laws</t>
+          <t>profile.sort.questions</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Прашања (2024–28)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Pyetje (2024–28)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Questions (2024–28)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>profile.sort.amendments</t>
+          <t>profile.sort.attendance</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>profile.sort.committees</t>
+          <t>profile.sort.discussions</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>home.pageTitle</t>
+          <t>profile.sort.laws</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Парламентарни отворени податоци</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Të dhëna të hapura parlamentare</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Parliamentary open data</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>home.badge</t>
+          <t>profile.sort.amendments</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Собрание на Република Северна Македонија · 2024–2028</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>home.heroTitle</t>
+          <t>profile.sort.committees</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Интерактивен панел на отворени податоци</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Panel interaktiv i të dhënave të hapura</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Interactive open data dashboard</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>home.heroSubtitle</t>
+          <t>home.pageTitle</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>на Собранието на Република Северна Македонија</t>
+          <t>Парламентарни отворени податоци</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
+          <t>Të dhëna të hapura parlamentare</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>of the Assembly of the Republic of North Macedonia</t>
+          <t>Parliamentary open data</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>home.kpiQuestions</t>
+          <t>home.badge</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>Собрание на Република Северна Македонија · 2024–2028</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Pyetje deputetësh</t>
+          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>home.kpiQuestionsNote</t>
+          <t>home.heroTitle</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>590 одговорени</t>
+          <t>Интерактивен панел на отворени податоци</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>590 të përgjigjura</t>
+          <t>Panel interaktiv i të dhënave të hapura</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>590 answered</t>
+          <t>Interactive open data dashboard</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>home.kpiMPs</t>
+          <t>home.heroSubtitle</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>на Собранието на Република Северна Македонија</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>of the Assembly of the Republic of North Macedonia</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>home.kpiMPsNote</t>
+          <t>home.kpiQuestions</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Активен состав 2024–2028</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Përbërja aktive 2024–2028</t>
+          <t>Pyetje deputetësh</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Active assembly 2024–2028</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>home.kpiOffices</t>
+          <t>home.kpiQuestionsNote</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Канцеларии</t>
+          <t>590 одговорени</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>590 të përgjigjura</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Offices</t>
+          <t>590 answered</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>home.kpiOfficesNote</t>
+          <t>home.kpiMPs</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>за контакт со граѓани</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>për kontakt me qytetarët</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>for citizen contact</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>home.descQuestions</t>
+          <t>home.kpiMPsNote</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
+          <t>Активен состав 2024–2028</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
+          <t>Përbërja aktive 2024–2028</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
+          <t>Active assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>home.descMyMP</t>
+          <t>home.kpiOffices</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
+          <t>Канцеларии</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
+          <t>Offices</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>home.descOffices</t>
+          <t>home.kpiOfficesNote</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
+          <t>за контакт со граѓани</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
+          <t>për kontakt me qytetarët</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
+          <t>for citizen contact</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>home.descProfile</t>
+          <t>home.descQuestions</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
+          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
+          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Unified MP profile: parliamentary activity and citizen cases</t>
+          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>home.open</t>
+          <t>home.descMyMP</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Отвори</t>
+          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Hap</t>
+          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>home.disclaimerSupport</t>
+          <t>home.descOffices</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
+          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
+          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
+          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPre</t>
+          <t>home.descProfile</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Контролната табла користи податоци преземени од</t>
+          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Paneli përdor të dhëna të marra nga</t>
+          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>The dashboard uses data sourced from</t>
+          <t>Unified MP profile: parliamentary activity and citizen cases</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPost</t>
+          <t>home.open</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
+          <t>Отвори</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
+          <t>Hap</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>about.p1</t>
+          <t>home.disclaimerSupport</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
+          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
+          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
+          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>about.p2</t>
+          <t>home.disclaimerDataPre</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
+          <t>Контролната табла користи податоци преземени од</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
+          <t>Paneli përdor të dhëna të marra nga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
+          <t>The dashboard uses data sourced from</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>about.p3</t>
+          <t>home.disclaimerDataPost</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
+          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
+          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
+          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>about.goalsIntro</t>
+          <t>about.p1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
+          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
+          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>In pursuing our vision and mission, our long-term goals are:</t>
+          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>about.goals.0</t>
+          <t>about.p2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Балансиран социо економски развој</t>
+          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Zhvillim i balancuar socio-ekonomik</t>
+          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Balanced socio-economic development</t>
+          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>about.goals.1</t>
+          <t>about.p3</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Активна граѓанска вклученост</t>
+          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Përfshirje aktive qytetare</t>
+          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Active civic engagement</t>
+          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>about.goals.2</t>
+          <t>about.goalsIntro</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Партиципативна политичка култура</t>
+          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Kulturë politike participative</t>
+          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Participative political culture</t>
+          <t>In pursuing our vision and mission, our long-term goals are:</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>about.goals.3</t>
+          <t>about.goals.0</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Остварување на либерални вредности во општеството</t>
+          <t>Балансиран социо економски развој</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Realizimi i vlerave liberale në shoqëri</t>
+          <t>Zhvillim i balancuar socio-ekonomik</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Realising liberal values in society</t>
+          <t>Balanced socio-economic development</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>about.goals.4</t>
+          <t>about.goals.1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Почит кон владеење на правото и доброто владеење</t>
+          <t>Активна граѓанска вклученост</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
+          <t>Përfshirje aktive qytetare</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Respect for the rule of law and good governance</t>
+          <t>Active civic engagement</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>about.goals.5</t>
+          <t>about.goals.2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Промоција на одржливо образование</t>
+          <t>Партиципативна политичка култура</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Promovimi i arsimit të qëndrueshëm</t>
+          <t>Kulturë politike participative</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Promotion of sustainable education</t>
+          <t>Participative political culture</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>about.goals.6</t>
+          <t>about.goals.3</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
+          <t>Остварување на либерални вредности во општеството</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Realizimi i një procesi të vendimmarrjes së bazuar në dëshmi</t>
+          <t>Realizimi i vlerave liberale në shoqëri</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Achieving an evidence-based decision-making process</t>
+          <t>Realising liberal values in society</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>about.goals.7</t>
+          <t>about.goals.4</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Мултиетничко и мултикултурно сопостоење</t>
+          <t>Почит кон владеење на правото и доброто владеење</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bashkëjetesë multietnike dhe multikulturore</t>
+          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Multi-ethnic and multicultural coexistence</t>
+          <t>Respect for the rule of law and good governance</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>project.p1</t>
+          <t>about.goals.5</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
+          <t>Промоција на одржливо образование</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
+          <t>Promovimi i arsimit të qëndrueshëm</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
+          <t>Promotion of sustainable education</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>project.p2</t>
+          <t>about.goals.6</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
+          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
+          <t>Realizimi i një procesi të vendimmarrjes së bazuar në dëshmi</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
+          <t>Achieving an evidence-based decision-making process</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>project.p3</t>
+          <t>about.goals.7</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
+          <t>Мултиетничко и мултикултурно сопостоење</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
+          <t>Bashkëjetesë multietnike dhe multikulturore</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
+          <t>Multi-ethnic and multicultural coexistence</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>project.p4</t>
+          <t>project.p1</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество е поддржан преку грантовата шема Digital Spark, како дел од проектот Regional Support Mechanism EECA, спроведуван од Фондацијата Метаморфозис и TechSoup, во партнерство со CIVICUS и во рамки на Digital Democracy Initiative (DDI), која го опфаќа Глобалниот југ.</t>
+          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare mbështetet përmes skemës së granteve Digital Spark, si pjesë e projektit Regional Support Mechanism EECA, i zbatuar nga Fondacioni Metamorphosis dhe TechSoup, në partneritet me CIVICUS dhe në kuadër të Digital Democracy Initiative (DDI), e cila mbulon Jugun Global.</t>
+          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Assembly Open Data in Practice: Encouraging Citizen Participation, is supported through the Digital Spark granting scheme, as part of the Regional Support Mechanism EECA project, implemented by Metamorphosis Foundation and TechSoup, in partnership with CIVICUS and under the Digital Democracy Initiative (DDI) that covers the Global South.</t>
+          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>methodology.title</t>
+          <t>project.p2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Методологија</t>
+          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Metodologjia</t>
+          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>methodology.subtitle</t>
+          <t>project.p3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Извори, ограничувања и процес на освежување</t>
+          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
+          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Sources, limitations and the update process</t>
+          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>methodology.formatLabel</t>
+          <t>project.p4</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Формат</t>
+          <t>Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество е поддржан преку грантовата шема Digital Spark, како дел од проектот Regional Support Mechanism EECA, спроведуван од Фондацијата Метаморфозис и TechSoup, во партнерство со CIVICUS и во рамки на Digital Democracy Initiative (DDI), која го опфаќа Глобалниот југ.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Formati</t>
+          <t>Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare mbështetet përmes skemës së granteve Digital Spark, si pjesë e projektit Regional Support Mechanism EECA, i zbatuar nga Fondacioni Metamorphosis dhe TechSoup, në partneritet me CIVICUS dhe në kuadër të Digital Democracy Initiative (DDI), e cila mbulon Jugun Global.</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Assembly Open Data in Practice: Encouraging Citizen Participation, is supported through the Digital Spark granting scheme, as part of the Regional Support Mechanism EECA project, implemented by Metamorphosis Foundation and TechSoup, in partnership with CIVICUS and under the Digital Democracy Initiative (DDI) that covers the Global South.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>methodology.recordsLabel</t>
+          <t>methodology.title</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>записи</t>
+          <t>Методологија</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>regjistrime</t>
+          <t>Metodologjia</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>records</t>
+          <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>methodology.lastPortalUpdate</t>
+          <t>methodology.subtitle</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Последно освежување на порталот</t>
+          <t>Извори, ограничувања и процес на освежување</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Përditësimi i fundit i portalit</t>
+          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Last portal update</t>
+          <t>Sources, limitations and the update process</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>methodology.sources.0.name</t>
+          <t>methodology.formatLabel</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Пратенички прашања 2024–2028</t>
+          <t>Формат</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve 2024–2028</t>
+          <t>Formati</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Parliamentary questions 2024–2028</t>
+          <t>Format</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.0</t>
+          <t>methodology.recordsLabel</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
+          <t>записи</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
+          <t>regjistrime</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
+          <t>records</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.1</t>
+          <t>methodology.lastPortalUpdate</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
+          <t>Последно освежување на порталот</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
+          <t>Përditësimi i fundit i portalit</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
+          <t>Last portal update</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.2</t>
+          <t>methodology.sources.0.name</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
+          <t>Пратенички прашања 2024–2028</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
+          <t>Pyetjet e deputetëve 2024–2028</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>91 records have no assigned institution — addressed to independent bodies.</t>
+          <t>Parliamentary questions 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.3</t>
+          <t>methodology.sources.0.notes.0</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
+          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
+          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
+          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>methodology.sources.1.name</t>
+          <t>methodology.sources.0.notes.1</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
+          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
+          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
+          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.0</t>
+          <t>methodology.sources.0.notes.2</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
+          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
+          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Periodic report, not updated since November 2025.</t>
+          <t>91 records have no assigned institution — addressed to independent bodies.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.1</t>
+          <t>methodology.sources.0.notes.3</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
+          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
+          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>The XLSX file uses a three-row header structure with internal codes.</t>
+          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.2</t>
+          <t>methodology.sources.1.name</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
+          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
+          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
+          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>methodology.sources.2.name</t>
+          <t>methodology.sources.1.notes.0</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>Periodic report, not updated since November 2025.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.0</t>
+          <t>methodology.sources.1.notes.1</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
+          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
+          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
+          <t>The XLSX file uses a three-row header structure with internal codes.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.1</t>
+          <t>methodology.sources.1.notes.2</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
+          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
+          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Format: tidy/long — each category is a separate row.</t>
+          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.2</t>
+          <t>methodology.sources.2.name</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>The UUID identifier is used to join with the other datasets.</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyTitle</t>
+          <t>methodology.sources.2.notes.0</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Активен состав (120 пратеници)</t>
+          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Përbërja aktive (120 deputetë)</t>
+          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Active assembly (120 MPs)</t>
+          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP1</t>
+          <t>methodology.sources.2.notes.1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
+          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
+          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
+          <t>Format: tidy/long — each category is a separate row.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP2</t>
+          <t>methodology.sources.2.notes.2</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
+          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
+          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
+          <t>The UUID identifier is used to join with the other datasets.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>methodology.joinTitle</t>
+          <t>methodology.activeAssemblyTitle</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Поврзување на датасети</t>
+          <t>Активен состав (120 пратеници)</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Lidhja e dataseteve</t>
+          <t>Përbërja aktive (120 deputetë)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Joining the datasets</t>
+          <t>Active assembly (120 MPs)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>methodology.joinP1</t>
+          <t>methodology.activeAssemblyP1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
+          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
+          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
+          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>methodology.joinP2</t>
+          <t>methodology.activeAssemblyP2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
+          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
+          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
+          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>methodology.refreshTitle</t>
+          <t>methodology.joinTitle</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Процес на освежување</t>
+          <t>Поврзување на датасети</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Procesi i përditësimit</t>
+          <t>Lidhja e dataseteve</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Update process</t>
+          <t>Joining the datasets</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>methodology.refreshIntro</t>
+          <t>methodology.joinP1</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
+          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
+          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
+          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1pre</t>
+          <t>methodology.joinP2</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1post</t>
+          <t>methodology.refreshTitle</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ги презема новите датотеки од CKAN API.</t>
+          <t>Процес на освежување</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>i merr skedarët e rinj nga CKAN API.</t>
+          <t>Procesi i përditësimit</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>fetches the new files from the CKAN API.</t>
+          <t>Update process</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2pre</t>
+          <t>methodology.refreshIntro</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2post</t>
+          <t>methodology.refreshStep1pre</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ги обработува и генерира чисти JSON датотеки.</t>
+          <t>Скриптата</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
+          <t>Skripta</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>processes them and generates clean JSON files.</t>
+          <t>The script</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>methodology.refreshStep3</t>
+          <t>methodology.refreshStep1post</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+          <t>ги презема новите датотеки од CKAN API.</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+          <t>i merr skedarët e rinj nga CKAN API.</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>The system automatically rebuilds and deploys the dashboard.</t>
+          <t>fetches the new files from the CKAN API.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
+          <t>methodology.refreshStep2pre</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Скриптата</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Skripta</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>The script</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>methodology.refreshStep2post</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ги обработува и генерира чисти JSON датотеки.</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>processes them and generates clean JSON files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>methodology.refreshStep3</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>The system automatically rebuilds and deploys the dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
           <t>methodology.lastProcessedLabel</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Dashboard последно обработен:</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Paneli i përpunuar së fundi:</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>Dashboard last processed:</t>
         </is>

--- a/translations.xlsx
+++ b/translations.xlsx
@@ -2400,17 +2400,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>стапиле на должност по периодот на извештајот</t>
+          <t>стапиле по извештајниот период</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kanë marrë mandatin pas periudhës së raportit</t>
+          <t>morën mandat pas raportit</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>took office after the reporting period</t>
+          <t>seated after the report period</t>
         </is>
       </c>
     </row>

--- a/translations.xlsx
+++ b/translations.xlsx
@@ -3984,17 +3984,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>590 одговорени</t>
+          <t>одговорени</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>590 të përgjigjura</t>
+          <t>të përgjigjura</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>590 answered</t>
+          <t>answered</t>
         </is>
       </c>
     </row>
@@ -5062,17 +5062,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен (657), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
+          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен ({{total}}), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë (657), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
+          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë ({{total}}), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete (657), but the per-MP rankings cover only active members.</t>
+          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete ({{total}}), but the per-MP rankings cover only active members.</t>
         </is>
       </c>
     </row>

--- a/translations.xlsx
+++ b/translations.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1211,4108 +1211,4130 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>common.sessions</t>
+          <t>common.writtenAnswer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Седници</t>
+          <t>Писмен одговор</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seanca</t>
+          <t>Përgjigje me shkrim</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>Written answer</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>common.source</t>
+          <t>common.sessions</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Извор</t>
+          <t>Седници</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Burimi</t>
+          <t>Seanca</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Sessions</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>common.party</t>
+          <t>common.source</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Партија</t>
+          <t>Извор</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Partia</t>
+          <t>Burimi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Party</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>common.category</t>
+          <t>common.party</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Категорија</t>
+          <t>Партија</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kategoria</t>
+          <t>Partia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Party</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>common.subcategory</t>
+          <t>common.category</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Подкатегорија</t>
+          <t>Категорија</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nënkategoria</t>
+          <t>Kategoria</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>common.filter</t>
+          <t>common.subcategory</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Филтер</t>
+          <t>Подкатегорија</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Filtër</t>
+          <t>Nënkategoria</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Subcategory</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>common.sortBy</t>
+          <t>common.filter</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Сортирај по</t>
+          <t>Филтер</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rendit sipas</t>
+          <t>Filtër</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sort by</t>
+          <t>Filter</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>common.results</t>
+          <t>common.sortBy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>резултати</t>
+          <t>Сортирај по</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rezultate</t>
+          <t>Rendit sipas</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>Sort by</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>common.close</t>
+          <t>common.results</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Затвори</t>
+          <t>резултати</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mbyll</t>
+          <t>rezultate</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>results</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>common.prev</t>
+          <t>common.close</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Претходни</t>
+          <t>Затвори</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Të mëparshme</t>
+          <t>Mbyll</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Previous</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>common.next</t>
+          <t>common.prev</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Следни</t>
+          <t>Претходни</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Të mëtejshme</t>
+          <t>Të mëparshme</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Next</t>
+          <t>Previous</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>common.mpsLower</t>
+          <t>common.next</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>пратеници</t>
+          <t>Следни</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>deputetë</t>
+          <t>Të mëtejshme</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>Next</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>common.skipToContent</t>
+          <t>common.mpsLower</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Прескокни на содржината</t>
+          <t>пратеници</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kalo te përmbajtja</t>
+          <t>deputetë</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Skip to content</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>footer.dataNotePre</t>
+          <t>common.skipToContent</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Податоците се преземени од</t>
+          <t>Прескокни на содржината</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Të dhënat janë marrë nga</t>
+          <t>Kalo te përmbajtja</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Data is sourced from</t>
+          <t>Skip to content</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>footer.portalName</t>
+          <t>footer.dataNotePre</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Порталот за отворени податоци на Собранието на Република Северна Македонија</t>
+          <t>Податоците се преземени од</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut</t>
+          <t>Të dhënat janë marrë nga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>the Open Data Portal of the Assembly of the Republic of North Macedonia</t>
+          <t>Data is sourced from</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>footer.dataNotePost</t>
+          <t>footer.portalName</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>, во формата и содржината во која тие се објавени од Собранието.</t>
+          <t>Порталот за отворени податоци на Собранието на Република Северна Македонија</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
+          <t>Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>, in the form and content in which it is published by the Assembly.</t>
+          <t>the Open Data Portal of the Assembly of the Republic of North Macedonia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>questions.title</t>
+          <t>footer.dataNotePost</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>, во формата и содржината во која тие се објавени од Собранието.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve</t>
+          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>, in the form and content in which it is published by the Assembly.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>questions.subtitle</t>
+          <t>questions.title</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Прашања поставени во Собранието 2024–2028</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara në Kuvend 2024–2028</t>
+          <t>Pyetjet e deputetëve</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Questions raised in the Assembly 2024–2028</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>questions.kpiTotal</t>
+          <t>questions.subtitle</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Вкупно прашања</t>
+          <t>Прашања поставени во Собранието 2024–2028</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gjithsej pyetje</t>
+          <t>Pyetje të parashtruara në Kuvend 2024–2028</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Total questions</t>
+          <t>Questions raised in the Assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>questions.kpiAnswered</t>
+          <t>questions.kpiTotal</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Одговорени</t>
+          <t>Вкупно прашања</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Të përgjigjura</t>
+          <t>Gjithsej pyetje</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Answered</t>
+          <t>Total questions</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>questions.kpiPending</t>
+          <t>questions.kpiAnswered</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Во тек</t>
+          <t>Одговорени</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Në pritje</t>
+          <t>Të përgjigjura</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Answered</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>questions.kpiSessions</t>
+          <t>questions.kpiPending</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Опфатени седници</t>
+          <t>Во тек</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seanca të përfshira</t>
+          <t>Në pritje</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sessions covered</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>questions.chartByMP</t>
+          <t>questions.kpiSessions</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Прашања по пратеник</t>
+          <t>Опфатени седници</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pyetje sipas deputetit</t>
+          <t>Seanca të përfshira</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Questions by MP</t>
+          <t>Sessions covered</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>questions.chartByInstitution</t>
+          <t>questions.chartByMP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Прашања по институција</t>
+          <t>Прашања по пратеник</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pyetje sipas institucionit</t>
+          <t>Pyetje sipas deputetit</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Questions by institution</t>
+          <t>Questions by MP</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>questions.chartAnsweredVsPending</t>
+          <t>questions.chartByInstitution</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Одговорени наспроти во тек — по институција</t>
+          <t>Прашања по институција</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Të përgjigjura kundrejt në pritje — sipas institucionit</t>
+          <t>Pyetje sipas institucionit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Answered vs. pending — by institution</t>
+          <t>Questions by institution</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>questions.chartAnswerRate</t>
+          <t>questions.chartAnsweredVsPending</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Стапка на одговарање по институција</t>
+          <t>Одговорени наспроти во тек — по институција</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Shkalla e përgjigjes sipas institucionit</t>
+          <t>Të përgjigjura kundrejt në pritje — sipas institucionit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Answer rate by institution</t>
+          <t>Answered vs. pending — by institution</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>questions.chartAnswerRateNote</t>
+          <t>questions.chartAnswerRate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Сортирани по најмала стапка — кои институции ги одложуваат одговорите</t>
+          <t>Стапка на одговарање по институција</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Të renditura sipas shkallës më të ulët — cilat institucione vonojnë përgjigjet</t>
+          <t>Shkalla e përgjigjes sipas institucionit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sorted by lowest rate — which institutions delay their answers</t>
+          <t>Answer rate by institution</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>questions.chartByParty</t>
+          <t>questions.chartAnswerRateNote</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Прашања по партија</t>
+          <t>Сортирани по најмала стапка — кои институции ги одложуваат одговорите</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pyetje sipas grupit parlamentar</t>
+          <t>Të renditura sipas shkallës më të ulët — cilat institucione vonojnë përgjigjet</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Questions by party</t>
+          <t>Sorted by lowest rate — which institutions delay their answers</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>questions.chartByPartyNote</t>
+          <t>questions.chartByParty</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Вкупно прашања по партија, со стапка на одговарање</t>
+          <t>Прашања по партија</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gjithsej pyetje sipas partisë, me shkallën e përgjigjes</t>
+          <t>Pyetje sipas grupit parlamentar</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Total questions by party, with answer rate</t>
+          <t>Questions by party</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>questions.chartTimeline</t>
+          <t>questions.chartByPartyNote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Прашања по седница</t>
+          <t>Вкупно прашања по партија, со стапка на одговарање</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pyetje sipas seancës</t>
+          <t>Gjithsej pyetje sipas partisë, me shkallën e përgjigjes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Questions by session</t>
+          <t>Total questions by party, with answer rate</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>questions.sessionFull</t>
+          <t>questions.chartTimeline</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Седница бр.</t>
+          <t>Прашања по седница</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seanca nr.</t>
+          <t>Pyetje sipas seancës</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Session no.</t>
+          <t>Questions by session</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>questions.questionsShort</t>
+          <t>questions.sessionFull</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>прашања</t>
+          <t>Седница бр.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>pyetje</t>
+          <t>Seanca nr.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Session no.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>questions.tableQuestion</t>
+          <t>questions.questionsShort</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Прашање</t>
+          <t>прашања</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pyetje</t>
+          <t>pyetje</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>questions</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>questions.tableFrom</t>
+          <t>questions.tableQuestion</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Пратеник</t>
+          <t>Прашање</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Deputeti</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Question</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>questions.tableTo</t>
+          <t>questions.tableFrom</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Институција</t>
+          <t>Пратеник</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Institucioni</t>
+          <t>Deputeti</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Institution</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>questions.tableDate</t>
+          <t>questions.tableTo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Датум</t>
+          <t>Институција</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Institucioni</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Institution</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>questions.tableStatus</t>
+          <t>questions.tableDate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Датум</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Statusi</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>questions.detailTitle</t>
+          <t>questions.tableStatus</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Детали за прашањето</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Detajet e pyetjes</t>
+          <t>Statusi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Question details</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>questions.detailQuestion</t>
+          <t>questions.detailTitle</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Прашање</t>
+          <t>Детали за прашањето</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pyetja</t>
+          <t>Detajet e pyetjes</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Question details</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>questions.detailAnswer</t>
+          <t>questions.detailQuestion</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Одговор</t>
+          <t>Прашање</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Përgjigja</t>
+          <t>Pyetja</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>questions.detailNoAnswer</t>
+          <t>questions.detailAnswer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Одговорот сè уште не е доставен.</t>
+          <t>Одговор</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Përgjigja ende nuk është dorëzuar.</t>
+          <t>Përgjigja</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The answer has not been submitted yet.</t>
+          <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>questions.detailNoAnswerSource</t>
+          <t>questions.detailNoAnswer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Забелешка: Во изворните податоци објавени од Собранието, ова пратеничко прашање е означено како одговорено, но во полето предвидено за одговор повторно е ставен текстот на самото прашање.</t>
+          <t>Одговорот сè уште не е доставен.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shënim: Në të dhënat burimore të publikuara nga Kuvendi, kjo pyetje parlamentare është shënuar si e përgjigjur, por në fushën e parashikuar për përgjigje është vendosur përsëri teksti i vetë pyetjes.</t>
+          <t>Përgjigja ende nuk është dorëzuar.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Note: In the source data published by the Assembly, this parliamentary question is marked as answered, but the field intended for the answer again contains the text of the question itself.</t>
+          <t>The answer has not been submitted yet.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>questions.nullInstitution</t>
+          <t>questions.detailNoAnswerSource</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Независно тело</t>
+          <t>Забелешка: Во изворните податоци објавени од Собранието, ова пратеничко прашање е означено како одговорено, но во полето предвидено за одговор повторно е ставен текстот на самото прашање.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Organ i pavarur</t>
+          <t>Shënim: Në të dhënat burimore të publikuara nga Kuvendi, kjo pyetje parlamentare është shënuar si e përgjigjur, por në fushën e parashikuar për përgjigje është vendosur përsëri teksti i vetë pyetjes.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Independent body</t>
+          <t>Note: In the source data published by the Assembly, this parliamentary question is marked as answered, but the field intended for the answer again contains the text of the question itself.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>questions.nullDate</t>
+          <t>questions.nullInstitution</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Датумот не е назначен</t>
+          <t>Независно тело</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Data nuk është caktuar</t>
+          <t>Organ i pavarur</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Date not assigned</t>
+          <t>Independent body</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>questions.openDetailAria</t>
+          <t>questions.nullDate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Отвори детали за прашање од</t>
+          <t>Датумот не е назначен</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hap detajet e pyetjes nga</t>
+          <t>Data nuk është caktuar</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Open question details from</t>
+          <t>Date not assigned</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>questions.session</t>
+          <t>questions.openDetailAria</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Седница</t>
+          <t>Отвори детали за прашање од</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seanca</t>
+          <t>Hap detajet e pyetjes nga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Open question details from</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>questions.autoTranslated</t>
+          <t>questions.session</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Автоматски превод</t>
+          <t>Седница</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Përkthim automatik</t>
+          <t>Seanca</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Machine-translated</t>
+          <t>Session</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>questions.aiTranslationNotice</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>questions.autoTranslated</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Автоматски превод</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Përkthimi në gjuhën shqipe i pyetjeve parlamentare është përgatitur me ndihmën e mjeteve të inteligjencës artificiale (AI), duke u bazuar në materialet e disponueshme në gjuhën maqedonase në Portalin e të Dhënave të Hapura të Kuvendit. Deri në ditën e publikimit, materialet në portal ishin të disponueshme vetëm në gjuhën maqedonase.</t>
+          <t>Përkthim automatik</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>The English translation of the parliamentary questions was prepared using artificial intelligence (AI) tools, based on the materials available in Macedonian on the Assembly Open Data Portal. As of the date of publication, the materials on the portal were available only in Macedonian.</t>
+          <t>Machine-translated</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mymp.title</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Активност на пратеник</t>
-        </is>
-      </c>
+          <t>questions.aiTranslationNotice</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetit</t>
+          <t>Përkthimi në gjuhën shqipe i pyetjeve parlamentare është përgatitur me ndihmën e mjeteve të inteligjencës artificiale (AI), duke u bazuar në materialet e disponueshme në gjuhën maqedonase në Portalin e të Dhënave të Hapura të Kuvendit. Deri në ditën e publikimit, materialet në portal ishin të disponueshme vetëm në gjuhën maqedonase.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MP activity</t>
+          <t>The English translation of the parliamentary questions was prepared using artificial intelligence (AI) tools, based on the materials available in Macedonian on the Assembly Open Data Portal. As of the date of publication, the materials on the portal were available only in Macedonian.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mymp.subtitle</t>
+          <t>mymp.title</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
+          <t>Активност на пратеник</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
+          <t>Aktiviteti i deputetit</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MP activity for the period January–June 2025</t>
+          <t>MP activity</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mymp.stalenessNote</t>
+          <t>mymp.subtitle</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
+          <t>Активност на пратениците за периодот јануари–јуни 2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
+          <t>Aktiviteti i deputetëve për periudhën janar–qershor 2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
+          <t>MP activity for the period January–June 2025</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mymp.mostActiveTitle</t>
+          <t>mymp.stalenessNote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Најактивен пратеник</t>
+          <t>Извештајот е последно освежен во ноември 2025. Податоците се преземени од Порталот за отворени податоци на Собранието на Република Северна Македонија, во формата и содржината во која тие се објавени од Собранието.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Deputeti më aktiv</t>
+          <t>Raporti është përditësuar për herë të fundit në nëntor 2025. Të dhënat janë marrë nga Portali i të dhënave të hapura të Kuvendit të Republikës së Maqedonisë së Veriut, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Most active MP</t>
+          <t>The report was last updated in November 2025. Data is sourced from the Open Data Portal of the Assembly of the Republic of North Macedonia, in the form and content in which it is published by the Assembly.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mymp.mostActiveNote</t>
+          <t>mymp.mostActiveTitle</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
+          <t>Најактивен пратеник</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
+          <t>Deputeti më aktiv</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
+          <t>Most active MP</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mymp.kpiMPs</t>
+          <t>mymp.mostActiveNote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>Рангирано по нормализирана активност низ сите категории · јан–јун 2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>Renditur sipas aktivitetit të normalizuar në të gjitha kategoritë · jan–qer 2025</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>Ranked by normalised activity across all categories · Jan–Jun 2025</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mymp.newlySeatedNote</t>
+          <t>mymp.kpiMPs</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>стапиле по извештајниот период</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>morën mandat pas raportit</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>seated after the report period</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mymp.noPeriodData</t>
+          <t>mymp.newlySeatedNote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Стапил на должност по последниот извештај за активност</t>
+          <t>стапиле по извештајниот период</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
+          <t>morën mandat pas raportit</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Took office after the latest activity report</t>
+          <t>seated after the report period</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mymp.kpiAvgAttendance</t>
+          <t>mymp.noPeriodData</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Просечно присуство</t>
+          <t>Стапил на должност по последниот извештај за активност</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prezenca mesatare</t>
+          <t>Ka marrë mandatin pas raportit të fundit të aktivitetit</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Average attendance</t>
+          <t>Took office after the latest activity report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mymp.kpiZeroQuestions</t>
+          <t>mymp.kpiAvgAttendance</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Пратеници без прашања</t>
+          <t>Просечно присуство</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Deputetë pa pyetje</t>
+          <t>Prezenca mesatare</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MPs with no questions</t>
+          <t>Average attendance</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mymp.chartAttendance</t>
+          <t>mymp.kpiZeroQuestions</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Пратеници без прашања</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Deputetë pa pyetje</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>MPs with no questions</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mymp.chartDiscussions</t>
+          <t>mymp.chartAttendance</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mymp.chartQuestions</t>
+          <t>mymp.chartDiscussions</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mymp.colMP</t>
+          <t>mymp.chartQuestions</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Пратеник</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Deputeti</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mymp.colAttendance</t>
+          <t>mymp.colMP</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Пратеник</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Deputeti</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mymp.colExcused</t>
+          <t>mymp.colAttendance</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Оправдано отсуство</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mungesë e arsyetuar</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Excused absence</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mymp.colUnexcused</t>
+          <t>mymp.colExcused</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Неоправдано отсуство</t>
+          <t>Оправдано отсуство</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mungesa e pa arsyetuar</t>
+          <t>Mungesë e arsyetuar</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Unexcused absence</t>
+          <t>Excused absence</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mymp.colDiscussions</t>
+          <t>mymp.colUnexcused</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Неоправдано отсуство</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Mungesa e pa arsyetuar</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Unexcused absence</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mymp.colLaws</t>
+          <t>mymp.colDiscussions</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mymp.colAmendments</t>
+          <t>mymp.colLaws</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mymp.colQuestions</t>
+          <t>mymp.colAmendments</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Прашања</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pyetje</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mymp.colCommittees</t>
+          <t>mymp.colQuestions</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Прашања</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Pyetje</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Questions</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mymp.zeroQuestionsLabel</t>
+          <t>mymp.colCommittees</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Пратеници кои не поставиле ниту едно прашање</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>MPs who asked no questions at all</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mymp.top5Title</t>
+          <t>mymp.zeroQuestionsLabel</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Топ 5 најактивни пратеници</t>
+          <t>Пратеници кои не поставиле ниту едно прашање</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Top 5 deputetët më aktivë</t>
+          <t>Deputetë që nuk kanë parashtruar asnjë pyetje</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Top 5 most active MPs</t>
+          <t>MPs who asked no questions at all</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mymp.top15Label</t>
+          <t>mymp.top5Title</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Топ 15 —</t>
+          <t>Топ 5 најактивни пратеници</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>Top 5 deputetët më aktivë</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Top 15 —</t>
+          <t>Top 5 most active MPs</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mymp.compositeLabel</t>
+          <t>mymp.top15Label</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Вкупна активност</t>
+          <t>Топ 15 —</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Top 15 —</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>Top 15 —</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>mymp.onlyZero</t>
+          <t>mymp.compositeLabel</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Само без прашања</t>
+          <t>Вкупна активност</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Vetëm pa pyetje</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Only without questions</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mymp.zeroSentence</t>
+          <t>mymp.onlyZero</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
+          <t>Само без прашања</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
+          <t>Vetëm pa pyetje</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
+          <t>Only without questions</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>mymp.periodLabel</t>
+          <t>mymp.zeroSentence</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Период</t>
+          <t>{count} од {total} пратеници не поставиле ниту едно прашање во периодот јануари–јуни 2025.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Periudha</t>
+          <t>{count} nga {total} deputetë nuk kanë parashtruar asnjë pyetje në periudhën janar–qershor 2025.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>{count} of {total} MPs asked no questions at all in the period January–June 2025.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>offices.title</t>
+          <t>mymp.periodLabel</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>Период</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>Periudha</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>Period</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>offices.subtitle</t>
+          <t>offices.title</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>offices.kpiCases</t>
+          <t>offices.subtitle</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Случаи</t>
+          <t>Статистики за граѓански случаи по канцеларии на пратеници · по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Raste</t>
+          <t>Statistika të rasteve të qytetarëve sipas zyrave të deputetëve · sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Statistics on citizen cases by MP contact offices · as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>offices.kpiMeetings</t>
+          <t>offices.kpiCases</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Средби</t>
+          <t>Случаи</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Takime</t>
+          <t>Raste</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Cases</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>offices.kpiEvents</t>
+          <t>offices.kpiMeetings</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Настани</t>
+          <t>Средби</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ngjarje</t>
+          <t>Takime</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Meetings</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>offices.kpiInitiatives</t>
+          <t>offices.kpiEvents</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Иницијативи</t>
+          <t>Настани</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Iniciativa</t>
+          <t>Ngjarje</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>Events</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>offices.chartByMP</t>
+          <t>offices.kpiInitiatives</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Случаи по пратеник</t>
+          <t>Иницијативи</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raste sipas deputetit</t>
+          <t>Iniciativa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cases by MP</t>
+          <t>Initiatives</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>offices.chartByType</t>
+          <t>offices.chartByMP</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Случаи по пратеник</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Raste sipas deputetit</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Cases by MP</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>offices.chartByParty</t>
+          <t>offices.chartByType</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Случаи по партија</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raste sipas partisë</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cases by party</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>offices.chartByGender</t>
+          <t>offices.chartByParty</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Случаи по пол</t>
+          <t>Случаи по партија</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Raste sipas gjinisë</t>
+          <t>Raste sipas partisë</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cases by gender</t>
+          <t>Cases by party</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>offices.chartByAge</t>
+          <t>offices.chartByGender</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Случаи по возрасна група</t>
+          <t>Случаи по пол</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Raste sipas grupmoshës</t>
+          <t>Raste sipas gjinisë</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cases by age group</t>
+          <t>Cases by gender</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>offices.chartByEthnicity</t>
+          <t>offices.chartByAge</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Случаи по етничка припадност</t>
+          <t>Случаи по возрасна група</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raste sipas përkatësisë etnike</t>
+          <t>Raste sipas grupmoshës</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cases by ethnicity</t>
+          <t>Cases by age group</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>offices.chartOverTime</t>
+          <t>offices.chartByEthnicity</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Случаи по период</t>
+          <t>Случаи по етничка припадност</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Raste sipas periudhës</t>
+          <t>Raste sipas përkatësisë etnike</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cases over time</t>
+          <t>Cases by ethnicity</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>offices.chartByAgeNote</t>
+          <t>offices.chartOverTime</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Случаи по возрасна група на граѓаните</t>
+          <t>Случаи по период</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Raste sipas grupmoshës së qytetarëve</t>
+          <t>Raste sipas periudhës</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cases by age group of citizens</t>
+          <t>Cases over time</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>offices.chartByEthnicityNote</t>
+          <t>offices.chartByAgeNote</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Случаи по етничка припадност на граѓаните</t>
+          <t>Случаи по возрасна група на граѓаните</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Raste sipas përkatësisë etnike të qytetarëve</t>
+          <t>Raste sipas grupmoshës së qytetarëve</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cases by ethnicity of citizens</t>
+          <t>Cases by age group of citizens</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>offices.male</t>
+          <t>offices.chartByEthnicityNote</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Машки</t>
+          <t>Случаи по етничка припадност на граѓаните</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Meshkuj</t>
+          <t>Raste sipas përkatësisë etnike të qytetarëve</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Cases by ethnicity of citizens</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>offices.female</t>
+          <t>offices.male</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Женски</t>
+          <t>Машки</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Femra</t>
+          <t>Meshkuj</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>offices.formerMP</t>
+          <t>offices.female</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>поранешен пратеник</t>
+          <t>Женски</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ish-deputet</t>
+          <t>Femra</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>former MP</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>map.title</t>
+          <t>offices.formerMP</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Локации на канцеларии</t>
+          <t>поранешен пратеник</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Vendndodhjet e zyrave</t>
+          <t>ish-deputet</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Office locations</t>
+          <t>former MP</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>map.locatedSuffix</t>
+          <t>map.title</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>лоцирани канцеларии на мапата</t>
+          <t>Локации на канцеларии</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>zyra të lokalizuara në hartë</t>
+          <t>Vendndodhjet e zyrave</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>offices located on the map</t>
+          <t>Office locations</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>map.popupTitle</t>
+          <t>map.locatedSuffix</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Канцеларија</t>
+          <t>лоцирани канцеларии на мапата</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>zyra të lokalizuara në hartë</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>offices located on the map</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>profile.title</t>
+          <t>map.popupTitle</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Профил на пратеник</t>
+          <t>Канцеларија</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Profili i deputetit</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>MP profile</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>profile.subtitle</t>
+          <t>profile.title</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
+          <t>Профил на пратеник</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
+          <t>Profili i deputetit</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
+          <t>MP profile</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>profile.sectionQuestions</t>
+          <t>profile.subtitle</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Парламентарни прашања</t>
+          <t>Прашања 2024–2028 · Активност јануари–јуни 2025 · Канцеларии по состојба со 8 јануари 2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pyetje parlamentare</t>
+          <t>Pyetje 2024–2028 · Aktiviteti janar–qershor 2025 · Zyrat sipas gjendjes më 8 janar 2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>Questions 2024–2028 · Activity January–June 2025 · Offices as of 8 January 2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>profile.sectionActivity</t>
+          <t>profile.sectionQuestions</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Активност во Собранието</t>
+          <t>Парламентарни прашања</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Aktiviteti në Kuvend</t>
+          <t>Pyetje parlamentare</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Activity in the Assembly</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>profile.sectionOffice</t>
+          <t>profile.sectionActivity</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Канцеларија за контакт</t>
+          <t>Активност во Собранието</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Zyra e kontaktit</t>
+          <t>Aktiviteti në Kuvend</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Contact office</t>
+          <t>Activity in the Assembly</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>profile.noOfficeData</t>
+          <t>profile.sectionOffice</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
+          <t>Канцеларија за контакт</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
+          <t>Zyra e kontaktit</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>This MP has no recorded citizen cases.</t>
+          <t>Contact office</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>profile.noQuestionsData</t>
+          <t>profile.noOfficeData</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
+          <t>Овој пратеник нема евидентирани граѓански случаи.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
+          <t>Ky deputet nuk ka raste të qytetarëve të evidentuara.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>This MP asked no questions in the current mandate.</t>
+          <t>This MP has no recorded citizen cases.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>profile.questionsAsked</t>
+          <t>profile.noQuestionsData</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Поставени прашања</t>
+          <t>Овој пратеник не поставил прашања во тековниот мандат.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara</t>
+          <t>Ky deputet nuk ka parashtruar pyetje në mandatin aktual.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>This MP asked no questions in the current mandate.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>profile.plenaryAttendance</t>
+          <t>profile.questionsAsked</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Присуство на пленарни седници</t>
+          <t>Поставени прашања</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Prezenca në seanca plenare</t>
+          <t>Pyetje të parashtruara</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Plenary session attendance</t>
+          <t>Questions asked</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>profile.committees</t>
+          <t>profile.plenaryAttendance</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Присуство на пленарни седници</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Prezenca në seanca plenare</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Plenary session attendance</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>profile.citizenCases</t>
+          <t>profile.committees</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Граѓански случаи</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Raste qytetare</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Citizen cases</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>profile.topInstitutions</t>
+          <t>profile.citizenCases</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Најчесто адресирани институции</t>
+          <t>Граѓански случаи</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Institucionet më të adresuara</t>
+          <t>Raste qytetare</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Most frequently addressed institutions</t>
+          <t>Citizen cases</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>profile.recentQuestions</t>
+          <t>profile.topInstitutions</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Последни прашања</t>
+          <t>Најчесто адресирани институции</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pyetjet e fundit</t>
+          <t>Institucionet më të adresuara</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Recent questions</t>
+          <t>Most frequently addressed institutions</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>profile.casesByType</t>
+          <t>profile.recentQuestions</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Случаи по тип</t>
+          <t>Последни прашања</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Raste sipas llojit</t>
+          <t>Pyetjet e fundit</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Cases by type</t>
+          <t>Recent questions</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>profile.independentBody</t>
+          <t>profile.casesByType</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Независно тело</t>
+          <t>Случаи по тип</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Organ i pavarur</t>
+          <t>Raste sipas llojit</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Independent body</t>
+          <t>Cases by type</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>profile.sort.name</t>
+          <t>profile.independentBody</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Абецеден ред</t>
+          <t>Независно тело</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Rend alfabetik</t>
+          <t>Organ i pavarur</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Alphabetical</t>
+          <t>Independent body</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>profile.sort.composite</t>
+          <t>profile.sort.name</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Општа активност</t>
+          <t>Абецеден ред</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Aktiviteti i përgjithshëm</t>
+          <t>Rend alfabetik</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Overall activity</t>
+          <t>Alphabetical</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>profile.sort.questions</t>
+          <t>profile.sort.composite</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Прашања (2024–28)</t>
+          <t>Општа активност</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Pyetje (2024–28)</t>
+          <t>Aktiviteti i përgjithshëm</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Questions (2024–28)</t>
+          <t>Overall activity</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>profile.sort.attendance</t>
+          <t>profile.sort.questions</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Присуство</t>
+          <t>Прашања (2024–28)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Prezenca</t>
+          <t>Pyetje (2024–28)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Questions (2024–28)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>profile.sort.discussions</t>
+          <t>profile.sort.attendance</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Дискусии</t>
+          <t>Присуство</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Diskutime</t>
+          <t>Prezenca</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Discussions</t>
+          <t>Attendance</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>profile.sort.laws</t>
+          <t>profile.sort.discussions</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Закони</t>
+          <t>Дискусии</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ligje</t>
+          <t>Diskutime</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Laws</t>
+          <t>Discussions</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>profile.sort.amendments</t>
+          <t>profile.sort.laws</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Амандмани</t>
+          <t>Закони</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Amendamente</t>
+          <t>Ligje</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Amendments</t>
+          <t>Laws</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>profile.sort.committees</t>
+          <t>profile.sort.amendments</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Комисии</t>
+          <t>Амандмани</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Komisione</t>
+          <t>Amendamente</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Committees</t>
+          <t>Amendments</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>home.pageTitle</t>
+          <t>profile.sort.committees</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Парламентарни отворени податоци</t>
+          <t>Комисии</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Të dhëna të hapura parlamentare</t>
+          <t>Komisione</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Parliamentary open data</t>
+          <t>Committees</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>home.badge</t>
+          <t>home.pageTitle</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Собрание на Република Северна Македонија · 2024–2028</t>
+          <t>Парламентарни отворени податоци</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
+          <t>Të dhëna të hapura parlamentare</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
+          <t>Parliamentary open data</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>home.heroTitle</t>
+          <t>home.badge</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Интерактивен панел на отворени податоци</t>
+          <t>Собрание на Република Северна Македонија · 2024–2028</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Panel interaktiv i të dhënave të hapura</t>
+          <t>Kuvendi i Republikës së Maqedonisë së Veriut · 2024–2028</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Interactive open data dashboard</t>
+          <t>Assembly of the Republic of North Macedonia · 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>home.heroSubtitle</t>
+          <t>home.heroTitle</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>на Собранието на Република Северна Македонија</t>
+          <t>Интерактивен панел на отворени податоци</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
+          <t>Panel interaktiv i të dhënave të hapura</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>of the Assembly of the Republic of North Macedonia</t>
+          <t>Interactive open data dashboard</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>home.kpiQuestions</t>
+          <t>home.heroSubtitle</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Пратенички прашања</t>
+          <t>на Собранието на Република Северна Македонија</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Pyetje deputetësh</t>
+          <t>i Kuvendit të Republikës së Maqedonisë së Veriut</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Parliamentary questions</t>
+          <t>of the Assembly of the Republic of North Macedonia</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>home.kpiQuestionsNote</t>
+          <t>home.kpiQuestions</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>одговорени</t>
+          <t>Пратенички прашања</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>të përgjigjura</t>
+          <t>Pyetje deputetësh</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>answered</t>
+          <t>Parliamentary questions</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>home.kpiMPs</t>
+          <t>home.kpiQuestionsNote</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Пратеници</t>
+          <t>одговорени</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Deputetë</t>
+          <t>të përgjigjura</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>MPs</t>
+          <t>answered</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>home.kpiMPsNote</t>
+          <t>home.kpiMPs</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Активен состав 2024–2028</t>
+          <t>Пратеници</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Përbërja aktive 2024–2028</t>
+          <t>Deputetë</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Active assembly 2024–2028</t>
+          <t>MPs</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>home.kpiOffices</t>
+          <t>home.kpiMPsNote</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Канцеларии</t>
+          <t>Активен состав 2024–2028</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Zyra</t>
+          <t>Përbërja aktive 2024–2028</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Offices</t>
+          <t>Active assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>home.kpiOfficesNote</t>
+          <t>home.kpiOffices</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>за контакт со граѓани</t>
+          <t>Канцеларии</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>për kontakt me qytetarët</t>
+          <t>Zyra</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>for citizen contact</t>
+          <t>Offices</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>home.descQuestions</t>
+          <t>home.kpiOfficesNote</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
+          <t>за контакт со граѓани</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
+          <t>për kontakt me qytetarët</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
+          <t>for citizen contact</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>home.descMyMP</t>
+          <t>home.descQuestions</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
+          <t>Прашања поставени до институции, министерства и независни тела во Собранието 2024–2028</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
+          <t>Pyetje të parashtruara institucioneve, ministrive dhe organeve të pavarura në Kuvendin 2024–2028</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
+          <t>Questions addressed to institutions, ministries and independent bodies in the Assembly 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>home.descOffices</t>
+          <t>home.descMyMP</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
+          <t>Присуство, дискусии, закони и амандмани — активност на секој пратеник</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
+          <t>Prezenca, diskutime, ligje dhe amendamente — aktiviteti i secilit deputet</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
+          <t>Attendance, discussions, laws and amendments — the activity of each MP</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>home.descProfile</t>
+          <t>home.descOffices</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
+          <t>Граѓански случаи, состаноци и иницијативи по канцеларии на пратеници</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
+          <t>Raste qytetare, takime dhe iniciativa sipas zyrave të deputetëve</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Unified MP profile: parliamentary activity and citizen cases</t>
+          <t>Citizen cases, meetings and initiatives by MP contact offices</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>home.open</t>
+          <t>home.descProfile</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Отвори</t>
+          <t>Обединет профил на пратеник: парламентарна активност и граѓански случаи</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hap</t>
+          <t>Profil i unifikuar i deputetit: aktiviteti parlamentar dhe rastet e qytetarëve</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Unified MP profile: parliamentary activity and citizen cases</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>home.disclaimerSupport</t>
+          <t>home.open</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
+          <t>Отвори</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
+          <t>Hap</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPre</t>
+          <t>home.disclaimerSupport</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Контролната табла користи податоци преземени од</t>
+          <t>Оваа активност е поддржана од Иницијативата за дигитална демократија на CIVICUS (CIVICUS Digital Democracy Initiative – DDI), а ја спроведува Институтот за демократија „Социетас Цивилис“ – Скопје.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Paneli përdor të dhëna të marra nga</t>
+          <t>Kjo veprimtari mbështetet nga Iniciativa për Demokraci Dixhitale e CIVICUS (CIVICUS Digital Democracy Initiative – DDI), dhe zbatohet nga Instituti për Demokraci „Societas Civilis“ – Shkup.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>The dashboard uses data sourced from</t>
+          <t>This activity is supported by the CIVICUS Digital Democracy Initiative (DDI) and is implemented by the Institute for Democracy “Societas Civilis” – Skopje.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>home.disclaimerDataPost</t>
+          <t>home.disclaimerDataPre</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
+          <t>Контролната табла користи податоци преземени од</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
+          <t>Paneli përdor të dhëna të marra nga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
+          <t>The dashboard uses data sourced from</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>about.p1</t>
+          <t>home.disclaimerDataPost</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
+          <t>, во формата и содржината во која тие се објавени од Собранието. Институтот за демократија ги презентира и визуелизира достапните податоци, без дополнителна измена или верификација на нивната содржина.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
+          <t>, në formën dhe përmbajtjen në të cilën janë publikuar nga Kuvendi. Instituti për Demokraci i prezanton dhe vizualizon të dhënat e disponueshme, pa ndryshim apo verifikim shtesë të përmbajtjes së tyre.</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
+          <t>, in the form and content in which it is published by the Assembly. The Institute for Democracy presents and visualises the available data, without further modification or verification of its content.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>about.p2</t>
+          <t>about.p1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
+          <t>На својот пат, ИДСЦС има визија за Македонија како високо развиена демократија на слободни и активни граѓани.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
+          <t>Në rrugëtimin e vet, IDSCS ka vizionin për Maqedoninë si një demokraci shumë të zhvilluar të qytetarëve të lirë dhe aktivë.</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
+          <t>On its journey, IDSCS envisions Macedonia as a highly developed democracy of free and active citizens.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>about.p3</t>
+          <t>about.p2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
+          <t>Мисијата на ИДСЦС е поддршка на развојот на демократските процеси преку промоција на креирање на политики базирани на истражување, анализи и консултација со засегнатите страни.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
+          <t>Misioni i IDSCS është mbështetja e zhvillimit të proceseve demokratike përmes promovimit të krijimit të politikave të bazuara në hulumtim, analiza dhe konsultim me palët e interesuara.</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
+          <t>The mission of IDSCS is to support the development of democratic processes through promoting policy-making based on research, analysis and consultation with stakeholders.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>about.goalsIntro</t>
+          <t>about.p3</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
+          <t>ИДСЦС го истражува развојот на доброто управување, владеењето на правото и европските интеграции на Македонија. ИДСЦС има мисија да ја помогне граѓанската вклученост во носењето на одлуки и да ја зајакне партиципативната политичка култура. Преку зајакнување на слободарските вредности, ИДСЦС придонесува на соживот помеѓу различностите.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
+          <t>IDSCS hulumton zhvillimin e qeverisjes së mirë, sundimit të së drejtës dhe integrimit evropian të Maqedonisë. IDSCS ka për mision të ndihmojë përfshirjen qytetare në vendimmarrje dhe të forcojë kulturën politike participative. Përmes forcimit të vlerave liridashëse, IDSCS kontribuon në bashkëjetesën mes diversiteteve.</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>In pursuing our vision and mission, our long-term goals are:</t>
+          <t>IDSCS researches the development of good governance, the rule of law and Macedonia's European integration. IDSCS has a mission to support citizen involvement in decision-making and to strengthen participative political culture. By reinforcing the values of freedom, IDSCS contributes to coexistence among diversities.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>about.goals.0</t>
+          <t>about.goalsIntro</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Балансиран социо економски развој</t>
+          <t>Во остварувањето на визијата и мисијата, наши долгорочни цели се:</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Zhvillim i balancuar socio-ekonomik</t>
+          <t>Në realizimin e vizionit dhe misionit, qëllimet tona afatgjata janë:</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Balanced socio-economic development</t>
+          <t>In pursuing our vision and mission, our long-term goals are:</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>about.goals.1</t>
+          <t>about.goals.0</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Активна граѓанска вклученост</t>
+          <t>Балансиран социо економски развој</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Përfshirje aktive qytetare</t>
+          <t>Zhvillim i balancuar socio-ekonomik</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Active civic engagement</t>
+          <t>Balanced socio-economic development</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>about.goals.2</t>
+          <t>about.goals.1</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Партиципативна политичка култура</t>
+          <t>Активна граѓанска вклученост</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Kulturë politike participative</t>
+          <t>Përfshirje aktive qytetare</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Participative political culture</t>
+          <t>Active civic engagement</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>about.goals.3</t>
+          <t>about.goals.2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Остварување на либерални вредности во општеството</t>
+          <t>Партиципативна политичка култура</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Realizimi i vlerave liberale në shoqëri</t>
+          <t>Kulturë politike participative</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Realising liberal values in society</t>
+          <t>Participative political culture</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>about.goals.4</t>
+          <t>about.goals.3</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Почит кон владеење на правото и доброто владеење</t>
+          <t>Остварување на либерални вредности во општеството</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
+          <t>Realizimi i vlerave liberale në shoqëri</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Respect for the rule of law and good governance</t>
+          <t>Realising liberal values in society</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>about.goals.5</t>
+          <t>about.goals.4</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Промоција на одржливо образование</t>
+          <t>Почит кон владеење на правото и доброто владеење</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Promovimi i arsimit të qëndrueshëm</t>
+          <t>Respekt ndaj sundimit të së drejtës dhe qeverisjes së mirë</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Promotion of sustainable education</t>
+          <t>Respect for the rule of law and good governance</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>about.goals.6</t>
+          <t>about.goals.5</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
+          <t>Промоција на одржливо образование</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Realizimi i një procesi të vendimmarrjes së bazuar në dëshmi</t>
+          <t>Promovimi i arsimit të qëndrueshëm</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Achieving an evidence-based decision-making process</t>
+          <t>Promotion of sustainable education</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>about.goals.7</t>
+          <t>about.goals.6</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Мултиетничко и мултикултурно сопостоење</t>
+          <t>Остварување на процес на донесување на одлуки заснован на докази</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bashkëjetesë multietnike dhe multikulturore</t>
+          <t>Realizimi i një procesi të vendimmarrjes së bazuar në dëshmi</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Multi-ethnic and multicultural coexistence</t>
+          <t>Achieving an evidence-based decision-making process</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>project.p1</t>
+          <t>about.goals.7</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
+          <t>Мултиетничко и мултикултурно сопостоење</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
+          <t>Bashkëjetesë multietnike dhe multikulturore</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
+          <t>Multi-ethnic and multicultural coexistence</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>project.p2</t>
+          <t>project.p1</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
+          <t>Отворените податоци се важна алатка за транспарентност, отчетност и граѓанско учество. Иако Собранието располага со портал за отворени податоци, дел од податоците се објавени во технички формати кои се тешки за користење од пошироката јавност. Ова го ограничува нивниот потенцијал за информирање, анализа и јавен надзор.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
+          <t>Të dhënat e hapura janë një mjet i rëndësishëm për transparencë, llogaridhënie dhe pjesëmarrje qytetare. Edhe pse Kuvendi disponon një portal të të dhënave të hapura, një pjesë e të dhënave publikohen në formate teknike që janë të vështira për t'u përdorur nga publiku i gjerë. Kjo kufizon potencialin e tyre për informim, analizë dhe mbikëqyrje publike.</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
+          <t>Open data is an important tool for transparency, accountability and citizen participation. Although the Assembly has an open data portal, some of the data is published in technical formats that are difficult for the general public to use. This limits its potential for information, analysis and public oversight.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>project.p3</t>
+          <t>project.p2</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
+          <t>Проектот „Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество“ има за цел да ги приближи собраниските отворени податоци до граѓаните, медиумите, граѓанските организации, студентите и младите. Проектот комбинира развој на кориснички ориентиран dashboard, практична обука за користење на отворени податоци, дигитална кампања и застапување за одржливост на решението.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
+          <t>Projekti „Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare“ synon t'i afrojë të dhënat e hapura të Kuvendit te qytetarët, mediat, organizatat qytetare, studentët dhe të rinjtë. Projekti kombinon zhvillimin e një paneli të orientuar nga përdoruesi, trajnim praktik për përdorimin e të dhënave të hapura, fushatë dixhitale dhe avokim për qëndrueshmërinë e zgjidhjes.</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
+          <t>The project “Assembly Open Data in Practice: Encouraging Citizen Participation” aims to bring the Assembly's open data closer to citizens, the media, civil society organisations, students and young people. The project combines the development of a user-oriented dashboard, practical training in using open data, a digital campaign and advocacy for the sustainability of the solution.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>project.p4</t>
+          <t>project.p3</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество е поддржан преку грантовата шема Digital Spark, како дел од проектот Regional Support Mechanism EECA, спроведуван од Фондацијата Метаморфозис и TechSoup, во партнерство со CIVICUS и во рамки на Digital Democracy Initiative (DDI), која го опфаќа Глобалниот југ.</t>
+          <t>Преку проектот ќе се визуелизираат и систематизираат избрани податоци поврзани со пратенички прашања, платформата „Мој пратеник“ и канцелариите за контакт со граѓаните. Истовремено, проектот ќе ги зајакне капацитетите на корисниците за пристапување, толкување и користење на отворени податоци за следење на работата на Собранието и поттикнување поголема јавна отчетност.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare mbështetet përmes skemës së granteve Digital Spark, si pjesë e projektit Regional Support Mechanism EECA, i zbatuar nga Fondacioni Metamorphosis dhe TechSoup, në partneritet me CIVICUS dhe në kuadër të Digital Democracy Initiative (DDI), e cila mbulon Jugun Global.</t>
+          <t>Përmes projektit do të vizualizohen dhe sistematizohen të dhëna të zgjedhura të lidhura me pyetjet e deputetëve, platformën „Deputeti im“ dhe zyrat e kontaktit me qytetarët. Njëkohësisht, projekti do të forcojë kapacitetet e përdoruesve për qasjen, interpretimin dhe përdorimin e të dhënave të hapura për ndjekjen e punës së Kuvendit dhe nxitjen e një llogaridhënieje më të madhe publike.</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Assembly Open Data in Practice: Encouraging Citizen Participation, is supported through the Digital Spark granting scheme, as part of the Regional Support Mechanism EECA project, implemented by Metamorphosis Foundation and TechSoup, in partnership with CIVICUS and under the Digital Democracy Initiative (DDI) that covers the Global South.</t>
+          <t>Through the project, selected data related to parliamentary questions, the “My MP” platform and the citizen contact offices will be visualised and systematised. At the same time, the project will strengthen users' capacities to access, interpret and use open data to monitor the work of the Assembly and encourage greater public accountability.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>methodology.title</t>
+          <t>project.p4</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Методологија</t>
+          <t>Отворени податоци на Собранието во пракса: Поттикнување граѓанско учество е поддржан преку грантовата шема Digital Spark, како дел од проектот Regional Support Mechanism EECA, спроведуван од Фондацијата Метаморфозис и TechSoup, во партнерство со CIVICUS и во рамки на Digital Democracy Initiative (DDI), која го опфаќа Глобалниот југ.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Metodologjia</t>
+          <t>Të dhënat e hapura të Kuvendit në praktikë: Nxitja e pjesëmarrjes qytetare mbështetet përmes skemës së granteve Digital Spark, si pjesë e projektit Regional Support Mechanism EECA, i zbatuar nga Fondacioni Metamorphosis dhe TechSoup, në partneritet me CIVICUS dhe në kuadër të Digital Democracy Initiative (DDI), e cila mbulon Jugun Global.</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Assembly Open Data in Practice: Encouraging Citizen Participation, is supported through the Digital Spark granting scheme, as part of the Regional Support Mechanism EECA project, implemented by Metamorphosis Foundation and TechSoup, in partnership with CIVICUS and under the Digital Democracy Initiative (DDI) that covers the Global South.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>methodology.subtitle</t>
+          <t>methodology.title</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Извори, ограничувања и процес на освежување</t>
+          <t>Методологија</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
+          <t>Metodologjia</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Sources, limitations and the update process</t>
+          <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>methodology.formatLabel</t>
+          <t>methodology.subtitle</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Формат</t>
+          <t>Извори, ограничувања и процес на освежување</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Formati</t>
+          <t>Burimet, kufizimet dhe procesi i përditësimit</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Sources, limitations and the update process</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>methodology.recordsLabel</t>
+          <t>methodology.formatLabel</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>записи</t>
+          <t>Формат</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>regjistrime</t>
+          <t>Formati</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>records</t>
+          <t>Format</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>methodology.lastPortalUpdate</t>
+          <t>methodology.recordsLabel</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Последно освежување на порталот</t>
+          <t>записи</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Përditësimi i fundit i portalit</t>
+          <t>regjistrime</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Last portal update</t>
+          <t>records</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>methodology.sources.0.name</t>
+          <t>methodology.lastPortalUpdate</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Пратенички прашања 2024–2028</t>
+          <t>Последно освежување на порталот</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Pyetjet e deputetëve 2024–2028</t>
+          <t>Përditësimi i fundit i portalit</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Parliamentary questions 2024–2028</t>
+          <t>Last portal update</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.0</t>
+          <t>methodology.sources.0.name</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
+          <t>Пратенички прашања 2024–2028</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
+          <t>Pyetjet e deputetëve 2024–2028</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
+          <t>Parliamentary questions 2024–2028</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.1</t>
+          <t>methodology.sources.0.notes.0</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
+          <t>Датумите се во .NET legacy формат /Date(ms)/ — конвертирани во ISO-8601.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
+          <t>Datat janë në formatin legacy .NET /Date(ms)/ — të konvertuara në ISO-8601.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
+          <t>Dates are in the .NET legacy format /Date(ms)/ — converted to ISO-8601.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.2</t>
+          <t>methodology.sources.0.notes.1</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
+          <t>168 записи (26%) немаат назначена седница — прашањата сè уште не се распоредени.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
+          <t>168 regjistrime (26%) nuk kanë seancë të caktuar — pyetjet ende nuk janë renditur.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>91 records have no assigned institution — addressed to independent bodies.</t>
+          <t>168 records (26%) have no assigned session — the questions are not yet scheduled.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>methodology.sources.0.notes.3</t>
+          <t>methodology.sources.0.notes.2</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
+          <t>91 записи немаат назначена институција — адресирани до независни тела.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
+          <t>91 regjistrime nuk kanë institucion të caktuar — të adresuara organeve të pavarura.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
+          <t>91 records have no assigned institution — addressed to independent bodies.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>methodology.sources.1.name</t>
+          <t>methodology.sources.0.notes.3</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
+          <t>5 записи со статус 'Одговорено' имаат празен одговор — ограничување на изворните податоци.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
+          <t>5 regjistrime me status 'Përgjigjur' kanë përgjigje bosh — kufizim i të dhënave burimore.</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
+          <t>5 records with status 'Answered' have an empty answer — a limitation of the source data.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.0</t>
+          <t>methodology.sources.1.name</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
+          <t>Мојот пратеник — Извештај бр. 32 (јан–јун 2025)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
+          <t>Deputeti im — Raporti nr. 32 (jan–qer 2025)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Periodic report, not updated since November 2025.</t>
+          <t>My MP — Report no. 32 (Jan–Jun 2025)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.1</t>
+          <t>methodology.sources.1.notes.0</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
+          <t>Периодичен извештај, не е освежуван од ноември 2025.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
+          <t>Raport periodik, nuk është përditësuar që nga nëntori 2025.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The XLSX file uses a three-row header structure with internal codes.</t>
+          <t>Periodic report, not updated since November 2025.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>methodology.sources.1.notes.2</t>
+          <t>methodology.sources.1.notes.1</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
+          <t>XLSX датотеката користи тројна хедер структура со интерни кодови.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
+          <t>Skedari XLSX përdor një strukturë me tre rreshta header me kode të brendshme.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
+          <t>The XLSX file uses a three-row header structure with internal codes.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>methodology.sources.2.name</t>
+          <t>methodology.sources.1.notes.2</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Канцеларии за контакт со граѓани</t>
+          <t>Парсерот ги мапира хедерите по вредност, не по позиција — за отпорност на промени во XLSX структурата.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Zyrat e kontaktit me qytetarët</t>
+          <t>Parsuesi i mapon header-ët sipas vlerës, jo sipas pozitës — për qëndrueshmëri ndaj ndryshimeve në strukturën XLSX.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Citizen contact offices</t>
+          <t>The parser maps headers by value, not by position — for resilience against changes in the XLSX structure.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.0</t>
+          <t>methodology.sources.2.name</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
+          <t>Канцеларии за контакт со граѓани</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
+          <t>Zyrat e kontaktit me qytetarët</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
+          <t>Citizen contact offices</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.1</t>
+          <t>methodology.sources.2.notes.0</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
+          <t>Опфаќа 46 пратеници (не сите 120) — само оние со активни канцеларии.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
+          <t>Përfshin 46 deputetë (jo të gjithë 120) — vetëm ata me zyra aktive.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Format: tidy/long — each category is a separate row.</t>
+          <t>Covers 46 MPs (not all 120) — only those with active offices.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>methodology.sources.2.notes.2</t>
+          <t>methodology.sources.2.notes.1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
+          <t>Формат: tidy/long — секоја категорија е засебен ред.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
+          <t>Format: tidy/long — secila kategori është rresht i veçantë.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>The UUID identifier is used to join with the other datasets.</t>
+          <t>Format: tidy/long — each category is a separate row.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyTitle</t>
+          <t>methodology.sources.2.notes.2</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Активен состав (120 пратеници)</t>
+          <t>UUID идентификаторот се користи за поврзување со другите датасети.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Përbërja aktive (120 deputetë)</t>
+          <t>Identifikuesi UUID përdoret për lidhjen me datasetet e tjera.</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Active assembly (120 MPs)</t>
+          <t>The UUID identifier is used to join with the other datasets.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP1</t>
+          <t>methodology.activeAssemblyTitle</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
+          <t>Активен состав (120 пратеници)</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
+          <t>Përbërja aktive (120 deputetë)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
+          <t>Active assembly (120 MPs)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>methodology.activeAssemblyP2</t>
+          <t>methodology.activeAssemblyP1</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен ({{total}}), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
+          <t>Како единствен извор на вистина за тоа кој е пратеник се користи активниот состав на Собранието — точно 120 членови, преземени од официјалниот регистар на kancelarii.sobranie.mk (статус „активен“). Пратениците кои презедоа функција во Владата или како директори (чиј мандат мирува, пр. премиерот и министрите) и заменетите пратеници не се дел од овие 120 и се исклучени од сите прегледи по пратеник.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë ({{total}}), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
+          <t>Si burim i vetëm i së vërtetës për atë se kush është deputet përdoret përbërja aktive e Kuvendit — saktësisht 120 anëtarë, të marrë nga regjistri zyrtar i kancelarii.sobranie.mk (statusi „aktiv“). Deputetët që morën funksion në Qeveri ose si drejtorë (mandati i të cilëve është në qetësi, p.sh. kryeministri dhe ministrat) dhe deputetët e zëvendësuar nuk janë pjesë e këtyre 120 dhe përjashtohen nga të gjitha pamjet sipas deputetit.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete ({{total}}), but the per-MP rankings cover only active members.</t>
+          <t>The single source of truth for who is an MP is the active assembly of the Assembly — exactly 120 members, sourced from the official register at kancelarii.sobranie.mk (status “active”). MPs who took office in the Government or as directors (whose mandate is frozen, e.g. the prime minister and ministers) and replaced MPs are not part of these 120 and are excluded from all per-MP views.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>methodology.joinTitle</t>
+          <t>methodology.activeAssemblyP2</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Поврзување на датасети</t>
+          <t>Извештајот „Мојот пратеник“ се однесува на периодот јануари–јуни 2025; пратениците кои стапиле подоцна (замени) се прикажани во составот, но без податоци за тој период. Записот на пратенички прашања е задржан целосен ({{total}}), но ранг-листите по пратеник ги опфаќаат само активните членови.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Lidhja e dataseteve</t>
+          <t>Raporti „Deputeti im“ i referohet periudhës janar–qershor 2025; deputetët që morën mandatin më vonë (zëvendësime) shfaqen në përbërje, por pa të dhëna për atë periudhë. Regjistri i pyetjeve të deputetëve është mbajtur i plotë ({{total}}), por listat e renditjes sipas deputetit përfshijnë vetëm anëtarët aktivë.</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Joining the datasets</t>
+          <t>The “My MP” report covers the period January–June 2025; MPs who took office later (replacements) are shown in the assembly but without data for that period. The record of parliamentary questions is kept complete ({{total}}), but the per-MP rankings cover only active members.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>methodology.joinP1</t>
+          <t>methodology.joinTitle</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
+          <t>Поврзување на датасети</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
+          <t>Lidhja e dataseteve</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
+          <t>Joining the datasets</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>methodology.joinP2</t>
+          <t>methodology.joinP1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
+          <t>Канцелариите содржат UUID идентификатор на пратеник кој се совпаѓа 1:1 со официјалниот регистар и се користи како примарен клуч за поврзување. За другите датасети (имиња во различни формати) се применува детерминистичка нормализација на имиња со експлицитна табела на исклучоци за варијантни записи — без приближно (fuzzy) совпаѓање, за да се избегне погрешно поврзување на различни лица.</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
+          <t>Zyrat përmbajnë një identifikues UUID të deputetit që përputhet 1:1 me regjistrin zyrtar dhe përdoret si çelës primar për lidhjen. Për datasetet e tjera (emra në formate të ndryshme) zbatohet një normalizim deterministik i emrave me një tabelë eksplicite përjashtimesh për regjistrime variantesh — pa përputhje të përafërt (fuzzy), për të shmangur lidhjen e gabuar të personave të ndryshëm.</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
+          <t>The offices contain an MP UUID identifier that matches the official register 1:1 and is used as the primary join key. For the other datasets (names in different formats), a deterministic name normalisation is applied with an explicit exceptions table for variant records — without fuzzy matching, to avoid wrongly joining different people.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>methodology.refreshTitle</t>
+          <t>methodology.joinP2</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Процес на освежување</t>
+          <t>Профилот на пратеник ги обединува сите три датасети и покажува каде постојат, а каде недостасуваат податоци.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Procesi i përditësimit</t>
+          <t>Profili i deputetit i unifikon të tre datasetet dhe tregon ku ekzistojnë e ku mungojnë të dhënat.</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Update process</t>
+          <t>The MP profile unifies all three datasets and shows where data exists and where it is missing.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>methodology.refreshIntro</t>
+          <t>methodology.refreshTitle</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
+          <t>Процес на освежување</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
+          <t>Procesi i përditësimit</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
+          <t>Update process</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1pre</t>
+          <t>methodology.refreshIntro</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>Dashboard-от не користи live feed. Податоците се освежуваат рачно или преку автоматизирана скрипта 2–3 пати до март 2027. При секое освежување:</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>Paneli nuk përdor feed live. Të dhënat përditësohen manualisht ose përmes një skripti të automatizuar 2–3 herë deri në mars 2027. Në çdo përditësim:</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>The dashboard does not use a live feed. Data is refreshed manually or via an automated script 2–3 times until March 2027. On each refresh:</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>methodology.refreshStep1post</t>
+          <t>methodology.refreshStep1pre</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ги презема новите датотеки од CKAN API.</t>
+          <t>Скриптата</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>i merr skedarët e rinj nga CKAN API.</t>
+          <t>Skripta</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>fetches the new files from the CKAN API.</t>
+          <t>The script</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2pre</t>
+          <t>methodology.refreshStep1post</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Скриптата</t>
+          <t>ги презема новите датотеки од CKAN API.</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Skripta</t>
+          <t>i merr skedarët e rinj nga CKAN API.</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>The script</t>
+          <t>fetches the new files from the CKAN API.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>methodology.refreshStep2post</t>
+          <t>methodology.refreshStep2pre</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ги обработува и генерира чисти JSON датотеки.</t>
+          <t>Скриптата</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
+          <t>Skripta</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>processes them and generates clean JSON files.</t>
+          <t>The script</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>methodology.refreshStep3</t>
+          <t>methodology.refreshStep2post</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+          <t>ги обработува и генерира чисти JSON датотеки.</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+          <t>përpunon dhe gjeneron skedarë JSON të pastër.</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>The system automatically rebuilds and deploys the dashboard.</t>
+          <t>processes them and generates clean JSON files.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
+          <t>methodology.refreshStep3</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Системот автоматски го прегради и распоредува dashboard-от.</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Sistemi automatikisht e rindërton dhe e publikon panelin.</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>The system automatically rebuilds and deploys the dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
           <t>methodology.lastProcessedLabel</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>Dashboard последно обработен:</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>Paneli i përpunuar së fundi:</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>Dashboard last processed:</t>
         </is>
